--- a/research/traditional_assets/database/data/colombia/colombia_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_real_estate_operations_services.xlsx
@@ -1169,7 +1169,7 @@
         <v>0.0779744974384296</v>
       </c>
       <c r="R2">
-        <v>0.0703501470260436</v>
+        <v>0.0703501470260435</v>
       </c>
       <c r="S2">
         <v>0.0482023673444086</v>
@@ -1197,7 +1197,7 @@
         <v>0.96202326712867</v>
       </c>
       <c r="Z2">
-        <v>1.0485901482991</v>
+        <v>1.04859014829911</v>
       </c>
       <c r="AA2">
         <v>781.2</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08377496490093293</v>
+        <v>0.08351100252377967</v>
       </c>
       <c r="C2">
-        <v>1334.962097723404</v>
+        <v>1325.76366565051</v>
       </c>
       <c r="D2">
-        <v>1321.562097723404</v>
+        <v>1327.02866565051</v>
       </c>
       <c r="E2">
-        <v>-781.2</v>
+        <v>-766.5350000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14.665</v>
       </c>
       <c r="G2">
         <v>13.4</v>
@@ -1451,28 +1451,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7376495</v>
       </c>
       <c r="N2">
-        <v>213.5666666666667</v>
+        <v>212.8290171666667</v>
       </c>
       <c r="O2">
-        <v>74.74833333333332</v>
+        <v>74.49015600833333</v>
       </c>
       <c r="P2">
-        <v>138.8183333333333</v>
+        <v>138.3388611583333</v>
       </c>
       <c r="Q2">
-        <v>138.9183333333333</v>
+        <v>138.4388611583333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08377496490093293</v>
+        <v>0.08402429547856533</v>
       </c>
       <c r="T2">
-        <v>0.5525820103960152</v>
+        <v>0.5562100741006355</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>289.5232311099874</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08351100252377967</v>
+        <v>0.0832470401466264</v>
       </c>
       <c r="C3">
-        <v>1325.76366565051</v>
+        <v>1316.61064572928</v>
       </c>
       <c r="D3">
-        <v>1327.02866565051</v>
+        <v>1332.54064572928</v>
       </c>
       <c r="E3">
-        <v>-766.5350000000001</v>
+        <v>-751.87</v>
       </c>
       <c r="F3">
-        <v>14.665</v>
+        <v>29.33</v>
       </c>
       <c r="G3">
         <v>13.4</v>
@@ -1533,28 +1533,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M3">
-        <v>0.7376495</v>
+        <v>1.475299</v>
       </c>
       <c r="N3">
-        <v>212.8290171666667</v>
+        <v>212.0913676666667</v>
       </c>
       <c r="O3">
-        <v>74.49015600833333</v>
+        <v>74.23197868333332</v>
       </c>
       <c r="P3">
-        <v>138.3388611583333</v>
+        <v>137.8593889833333</v>
       </c>
       <c r="Q3">
-        <v>138.4388611583333</v>
+        <v>137.9593889833333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08402429547856533</v>
+        <v>0.08427871443533307</v>
       </c>
       <c r="T3">
-        <v>0.5562100741006355</v>
+        <v>0.5599121799216766</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>289.5232311099874</v>
+        <v>144.7616155549937</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0832470401466264</v>
+        <v>0.08298307776947313</v>
       </c>
       <c r="C4">
-        <v>1316.61064572928</v>
+        <v>1307.503606195162</v>
       </c>
       <c r="D4">
-        <v>1332.54064572928</v>
+        <v>1338.098606195162</v>
       </c>
       <c r="E4">
-        <v>-751.87</v>
+        <v>-737.205</v>
       </c>
       <c r="F4">
-        <v>29.33</v>
+        <v>43.995</v>
       </c>
       <c r="G4">
         <v>13.4</v>
@@ -1615,28 +1615,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M4">
-        <v>1.475299</v>
+        <v>2.2129485</v>
       </c>
       <c r="N4">
-        <v>212.0913676666667</v>
+        <v>211.3537181666667</v>
       </c>
       <c r="O4">
-        <v>74.23197868333332</v>
+        <v>73.97380135833332</v>
       </c>
       <c r="P4">
-        <v>137.8593889833333</v>
+        <v>137.3799168083333</v>
       </c>
       <c r="Q4">
-        <v>137.9593889833333</v>
+        <v>137.4799168083333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08427871443533307</v>
+        <v>0.08453837914378673</v>
       </c>
       <c r="T4">
-        <v>0.5599121799216766</v>
+        <v>0.5636906178215021</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>144.7616155549937</v>
+        <v>96.50774370332915</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08298307776947313</v>
+        <v>0.08271911539231987</v>
       </c>
       <c r="C5">
-        <v>1307.503606195162</v>
+        <v>1298.443124803638</v>
       </c>
       <c r="D5">
-        <v>1338.098606195162</v>
+        <v>1343.703124803638</v>
       </c>
       <c r="E5">
-        <v>-737.205</v>
+        <v>-722.5400000000001</v>
       </c>
       <c r="F5">
-        <v>43.995</v>
+        <v>58.66</v>
       </c>
       <c r="G5">
         <v>13.4</v>
@@ -1697,28 +1697,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M5">
-        <v>2.2129485</v>
+        <v>2.950598</v>
       </c>
       <c r="N5">
-        <v>211.3537181666667</v>
+        <v>210.6160686666666</v>
       </c>
       <c r="O5">
-        <v>73.97380135833332</v>
+        <v>73.71562403333333</v>
       </c>
       <c r="P5">
-        <v>137.3799168083333</v>
+        <v>136.9004446333333</v>
       </c>
       <c r="Q5">
-        <v>137.4799168083333</v>
+        <v>137.0004446333333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08453837914378673</v>
+        <v>0.08480345353366653</v>
       </c>
       <c r="T5">
-        <v>0.5636906178215021</v>
+        <v>0.5675477731775739</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>96.50774370332915</v>
+        <v>72.38080777749686</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08271911539231987</v>
+        <v>0.08245515301516659</v>
       </c>
       <c r="C6">
-        <v>1298.443124803638</v>
+        <v>1289.429789030433</v>
       </c>
       <c r="D6">
-        <v>1343.703124803638</v>
+        <v>1349.354789030433</v>
       </c>
       <c r="E6">
-        <v>-722.5400000000001</v>
+        <v>-707.875</v>
       </c>
       <c r="F6">
-        <v>58.66</v>
+        <v>73.325</v>
       </c>
       <c r="G6">
         <v>13.4</v>
@@ -1779,28 +1779,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M6">
-        <v>2.950598</v>
+        <v>3.6882475</v>
       </c>
       <c r="N6">
-        <v>210.6160686666666</v>
+        <v>209.8784191666667</v>
       </c>
       <c r="O6">
-        <v>73.71562403333333</v>
+        <v>73.45744670833334</v>
       </c>
       <c r="P6">
-        <v>136.9004446333333</v>
+        <v>136.4209724583333</v>
       </c>
       <c r="Q6">
-        <v>137.0004446333333</v>
+        <v>136.5209724583333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08480345353366653</v>
+        <v>0.08507410843701747</v>
       </c>
       <c r="T6">
-        <v>0.5675477731775739</v>
+        <v>0.5714861318042999</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>72.38080777749686</v>
+        <v>57.90464622199748</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08245515301516659</v>
+        <v>0.08219119063801333</v>
       </c>
       <c r="C7">
-        <v>1289.429789030433</v>
+        <v>1280.464196276796</v>
       </c>
       <c r="D7">
-        <v>1349.354789030433</v>
+        <v>1355.054196276796</v>
       </c>
       <c r="E7">
-        <v>-707.875</v>
+        <v>-693.21</v>
       </c>
       <c r="F7">
-        <v>73.325</v>
+        <v>87.99000000000001</v>
       </c>
       <c r="G7">
         <v>13.4</v>
@@ -1861,28 +1861,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M7">
-        <v>3.6882475</v>
+        <v>4.425897</v>
       </c>
       <c r="N7">
-        <v>209.8784191666667</v>
+        <v>209.1407696666667</v>
       </c>
       <c r="O7">
-        <v>73.45744670833334</v>
+        <v>73.19926938333333</v>
       </c>
       <c r="P7">
-        <v>136.4209724583333</v>
+        <v>135.9415002833333</v>
       </c>
       <c r="Q7">
-        <v>136.5209724583333</v>
+        <v>136.0415002833333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08507410843701747</v>
+        <v>0.08535052195533334</v>
       </c>
       <c r="T7">
-        <v>0.5714861318042999</v>
+        <v>0.5755082852954243</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>57.90464622199748</v>
+        <v>48.25387185166457</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08219119063801333</v>
+        <v>0.08192722826086007</v>
       </c>
       <c r="C8">
-        <v>1280.464196276796</v>
+        <v>1271.546954080005</v>
       </c>
       <c r="D8">
-        <v>1355.054196276796</v>
+        <v>1360.801954080005</v>
       </c>
       <c r="E8">
-        <v>-693.21</v>
+        <v>-678.5450000000001</v>
       </c>
       <c r="F8">
-        <v>87.98999999999999</v>
+        <v>102.655</v>
       </c>
       <c r="G8">
         <v>13.4</v>
@@ -1943,28 +1943,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M8">
-        <v>4.425896999999999</v>
+        <v>5.163546499999999</v>
       </c>
       <c r="N8">
-        <v>209.1407696666667</v>
+        <v>208.4031201666667</v>
       </c>
       <c r="O8">
-        <v>73.19926938333333</v>
+        <v>72.94109205833333</v>
       </c>
       <c r="P8">
-        <v>135.9415002833333</v>
+        <v>135.4620281083334</v>
       </c>
       <c r="Q8">
-        <v>136.0415002833333</v>
+        <v>135.5620281083334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08535052195533334</v>
+        <v>0.08563287985038717</v>
       </c>
       <c r="T8">
-        <v>0.5755082852954243</v>
+        <v>0.5796169367110889</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>48.25387185166458</v>
+        <v>41.36046158714107</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08192722826086007</v>
+        <v>0.08166326588370681</v>
       </c>
       <c r="C9">
-        <v>1271.546954080005</v>
+        <v>1262.678680329259</v>
       </c>
       <c r="D9">
-        <v>1360.801954080005</v>
+        <v>1366.598680329259</v>
       </c>
       <c r="E9">
-        <v>-678.5450000000001</v>
+        <v>-663.88</v>
       </c>
       <c r="F9">
-        <v>102.655</v>
+        <v>117.32</v>
       </c>
       <c r="G9">
         <v>13.4</v>
@@ -2025,28 +2025,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M9">
-        <v>5.163546500000001</v>
+        <v>5.901196</v>
       </c>
       <c r="N9">
-        <v>208.4031201666667</v>
+        <v>207.6654706666667</v>
       </c>
       <c r="O9">
-        <v>72.94109205833333</v>
+        <v>72.68291473333333</v>
       </c>
       <c r="P9">
-        <v>135.4620281083334</v>
+        <v>134.9825559333333</v>
       </c>
       <c r="Q9">
-        <v>135.5620281083334</v>
+        <v>135.0825559333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08563287985038717</v>
+        <v>0.08592137596055088</v>
       </c>
       <c r="T9">
-        <v>0.5796169367110889</v>
+        <v>0.5838149066357899</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>41.36046158714105</v>
+        <v>36.19040388874843</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08166326588370681</v>
+        <v>0.08139930350655354</v>
       </c>
       <c r="C10">
-        <v>1262.678680329259</v>
+        <v>1253.860003487098</v>
       </c>
       <c r="D10">
-        <v>1366.598680329259</v>
+        <v>1372.445003487098</v>
       </c>
       <c r="E10">
-        <v>-663.88</v>
+        <v>-649.215</v>
       </c>
       <c r="F10">
-        <v>117.32</v>
+        <v>131.985</v>
       </c>
       <c r="G10">
         <v>13.4</v>
@@ -2107,28 +2107,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M10">
-        <v>5.901196</v>
+        <v>6.638845499999999</v>
       </c>
       <c r="N10">
-        <v>207.6654706666667</v>
+        <v>206.9278211666667</v>
       </c>
       <c r="O10">
-        <v>72.68291473333333</v>
+        <v>72.42473740833333</v>
       </c>
       <c r="P10">
-        <v>134.9825559333333</v>
+        <v>134.5030837583333</v>
       </c>
       <c r="Q10">
-        <v>135.0825559333333</v>
+        <v>134.6030837583333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08592137596055088</v>
+        <v>0.08621621264456433</v>
       </c>
       <c r="T10">
-        <v>0.5838149066357899</v>
+        <v>0.5881051396357591</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.19040388874843</v>
+        <v>32.16924790110972</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08139930350655354</v>
+        <v>0.08113534112940027</v>
       </c>
       <c r="C11">
-        <v>1253.860003487098</v>
+        <v>1245.091562816545</v>
       </c>
       <c r="D11">
-        <v>1372.445003487098</v>
+        <v>1378.341562816545</v>
       </c>
       <c r="E11">
-        <v>-649.215</v>
+        <v>-634.5500000000001</v>
       </c>
       <c r="F11">
-        <v>131.985</v>
+        <v>146.65</v>
       </c>
       <c r="G11">
         <v>13.4</v>
@@ -2189,28 +2189,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M11">
-        <v>6.638845499999999</v>
+        <v>7.376494999999998</v>
       </c>
       <c r="N11">
-        <v>206.9278211666667</v>
+        <v>206.1901716666667</v>
       </c>
       <c r="O11">
-        <v>72.42473740833333</v>
+        <v>72.16656008333332</v>
       </c>
       <c r="P11">
-        <v>134.5030837583333</v>
+        <v>134.0236115833333</v>
       </c>
       <c r="Q11">
-        <v>134.6030837583333</v>
+        <v>134.1236115833333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08621621264456433</v>
+        <v>0.08651760125488919</v>
       </c>
       <c r="T11">
-        <v>0.5881051396357591</v>
+        <v>0.5924907111468385</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.16924790110972</v>
+        <v>28.95232311099875</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08113534112940027</v>
+        <v>0.08087137875224702</v>
       </c>
       <c r="C12">
-        <v>1245.091562816545</v>
+        <v>1236.374008614122</v>
       </c>
       <c r="D12">
-        <v>1378.341562816545</v>
+        <v>1384.289008614122</v>
       </c>
       <c r="E12">
-        <v>-634.5500000000001</v>
+        <v>-619.885</v>
       </c>
       <c r="F12">
-        <v>146.65</v>
+        <v>161.315</v>
       </c>
       <c r="G12">
         <v>13.4</v>
@@ -2271,28 +2271,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M12">
-        <v>7.376495</v>
+        <v>8.1141445</v>
       </c>
       <c r="N12">
-        <v>206.1901716666667</v>
+        <v>205.4525221666667</v>
       </c>
       <c r="O12">
-        <v>72.16656008333332</v>
+        <v>71.90838275833332</v>
       </c>
       <c r="P12">
-        <v>134.0236115833333</v>
+        <v>133.5441394083333</v>
       </c>
       <c r="Q12">
-        <v>134.1236115833333</v>
+        <v>133.6441394083333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08651760125488919</v>
+        <v>0.08682576264297417</v>
       </c>
       <c r="T12">
-        <v>0.5924907111468385</v>
+        <v>0.5969748348267063</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.95232311099874</v>
+        <v>26.32029373727158</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08087137875224702</v>
+        <v>0.08060741637509375</v>
       </c>
       <c r="C13">
-        <v>1236.374008614122</v>
+        <v>1227.708002448924</v>
       </c>
       <c r="D13">
-        <v>1384.289008614122</v>
+        <v>1390.288002448924</v>
       </c>
       <c r="E13">
-        <v>-619.885</v>
+        <v>-605.22</v>
       </c>
       <c r="F13">
-        <v>161.315</v>
+        <v>175.98</v>
       </c>
       <c r="G13">
         <v>13.4</v>
@@ -2353,28 +2353,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M13">
-        <v>8.1141445</v>
+        <v>8.851793999999998</v>
       </c>
       <c r="N13">
-        <v>205.4525221666667</v>
+        <v>204.7148726666667</v>
       </c>
       <c r="O13">
-        <v>71.90838275833332</v>
+        <v>71.65020543333333</v>
       </c>
       <c r="P13">
-        <v>133.5441394083333</v>
+        <v>133.0646672333334</v>
       </c>
       <c r="Q13">
-        <v>133.6441394083333</v>
+        <v>133.1646672333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08682576264297417</v>
+        <v>0.08714092769897017</v>
       </c>
       <c r="T13">
-        <v>0.5969748348267063</v>
+        <v>0.6015608704083892</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.32029373727158</v>
+        <v>24.12693592583229</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08060741637509375</v>
+        <v>0.08034345399794048</v>
       </c>
       <c r="C14">
-        <v>1227.708002448924</v>
+        <v>1219.094217407936</v>
       </c>
       <c r="D14">
-        <v>1390.288002448924</v>
+        <v>1396.339217407936</v>
       </c>
       <c r="E14">
-        <v>-605.22</v>
+        <v>-590.5550000000001</v>
       </c>
       <c r="F14">
-        <v>175.98</v>
+        <v>190.645</v>
       </c>
       <c r="G14">
         <v>13.4</v>
@@ -2435,28 +2435,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M14">
-        <v>8.851793999999998</v>
+        <v>9.5894435</v>
       </c>
       <c r="N14">
-        <v>204.7148726666667</v>
+        <v>203.9772231666667</v>
       </c>
       <c r="O14">
-        <v>71.65020543333333</v>
+        <v>71.39202810833334</v>
       </c>
       <c r="P14">
-        <v>133.0646672333334</v>
+        <v>132.5851950583333</v>
       </c>
       <c r="Q14">
-        <v>133.1646672333333</v>
+        <v>132.6851950583333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08714092769897017</v>
+        <v>0.08746333792866721</v>
       </c>
       <c r="T14">
-        <v>0.6015608704083892</v>
+        <v>0.6062523320953982</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.12693592583229</v>
+        <v>22.27101777769134</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08034345399794048</v>
+        <v>0.08007949162078723</v>
       </c>
       <c r="C15">
-        <v>1219.094217407936</v>
+        <v>1210.53333834779</v>
       </c>
       <c r="D15">
-        <v>1396.339217407936</v>
+        <v>1402.44333834779</v>
       </c>
       <c r="E15">
-        <v>-590.5550000000001</v>
+        <v>-575.89</v>
       </c>
       <c r="F15">
-        <v>190.645</v>
+        <v>205.31</v>
       </c>
       <c r="G15">
         <v>13.4</v>
@@ -2517,28 +2517,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M15">
-        <v>9.5894435</v>
+        <v>10.327093</v>
       </c>
       <c r="N15">
-        <v>203.9772231666667</v>
+        <v>203.2395736666667</v>
       </c>
       <c r="O15">
-        <v>71.39202810833334</v>
+        <v>71.13385078333333</v>
       </c>
       <c r="P15">
-        <v>132.5851950583333</v>
+        <v>132.1057228833333</v>
       </c>
       <c r="Q15">
-        <v>132.6851950583333</v>
+        <v>132.2057228833333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08746333792866721</v>
+        <v>0.08779324607068281</v>
       </c>
       <c r="T15">
-        <v>0.6062523320953982</v>
+        <v>0.6110528975425703</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.27101777769134</v>
+        <v>20.68023079357053</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08007949162078723</v>
+        <v>0.07981552924363396</v>
       </c>
       <c r="C16">
-        <v>1210.53333834779</v>
+        <v>1202.02606215315</v>
       </c>
       <c r="D16">
-        <v>1402.44333834779</v>
+        <v>1408.60106215315</v>
       </c>
       <c r="E16">
-        <v>-575.89</v>
+        <v>-561.225</v>
       </c>
       <c r="F16">
-        <v>205.31</v>
+        <v>219.975</v>
       </c>
       <c r="G16">
         <v>13.4</v>
@@ -2599,28 +2599,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M16">
-        <v>10.327093</v>
+        <v>11.0647425</v>
       </c>
       <c r="N16">
-        <v>203.2395736666667</v>
+        <v>202.5019241666667</v>
       </c>
       <c r="O16">
-        <v>71.13385078333333</v>
+        <v>70.87567345833332</v>
       </c>
       <c r="P16">
-        <v>132.1057228833333</v>
+        <v>131.6262507083333</v>
       </c>
       <c r="Q16">
-        <v>132.2057228833333</v>
+        <v>131.7262507083333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08779324607068281</v>
+        <v>0.08813091675721642</v>
       </c>
       <c r="T16">
-        <v>0.6110528975425703</v>
+        <v>0.6159664174708522</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.68023079357053</v>
+        <v>19.30154874066583</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07981552924363396</v>
+        <v>0.07955156686648068</v>
       </c>
       <c r="C17">
-        <v>1202.02606215315</v>
+        <v>1193.573098001931</v>
       </c>
       <c r="D17">
-        <v>1408.60106215315</v>
+        <v>1414.813098001931</v>
       </c>
       <c r="E17">
-        <v>-561.225</v>
+        <v>-546.5600000000001</v>
       </c>
       <c r="F17">
-        <v>219.975</v>
+        <v>234.64</v>
       </c>
       <c r="G17">
         <v>13.4</v>
@@ -2681,28 +2681,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M17">
-        <v>11.0647425</v>
+        <v>11.802392</v>
       </c>
       <c r="N17">
-        <v>202.5019241666667</v>
+        <v>201.7642746666667</v>
       </c>
       <c r="O17">
-        <v>70.87567345833332</v>
+        <v>70.61749613333333</v>
       </c>
       <c r="P17">
-        <v>131.6262507083333</v>
+        <v>131.1467785333333</v>
       </c>
       <c r="Q17">
-        <v>131.7262507083333</v>
+        <v>131.2467785333333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08813091675721642</v>
+        <v>0.08847662722200081</v>
       </c>
       <c r="T17">
-        <v>0.6159664174708522</v>
+        <v>0.6209969259688551</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.30154874066583</v>
+        <v>18.09520194437421</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07955156686648068</v>
+        <v>0.07928760448932741</v>
       </c>
       <c r="C18">
-        <v>1193.573098001931</v>
+        <v>1185.175167637576</v>
       </c>
       <c r="D18">
-        <v>1414.813098001931</v>
+        <v>1421.080167637576</v>
       </c>
       <c r="E18">
-        <v>-546.5600000000001</v>
+        <v>-531.895</v>
       </c>
       <c r="F18">
-        <v>234.64</v>
+        <v>249.305</v>
       </c>
       <c r="G18">
         <v>13.4</v>
@@ -2763,28 +2763,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M18">
-        <v>11.802392</v>
+        <v>12.5400415</v>
       </c>
       <c r="N18">
-        <v>201.7642746666667</v>
+        <v>201.0266251666667</v>
       </c>
       <c r="O18">
-        <v>70.61749613333333</v>
+        <v>70.35931880833333</v>
       </c>
       <c r="P18">
-        <v>131.1467785333333</v>
+        <v>130.6673063583333</v>
       </c>
       <c r="Q18">
-        <v>131.2467785333333</v>
+        <v>130.7673063583333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08847662722200081</v>
+        <v>0.08883066805943063</v>
       </c>
       <c r="T18">
-        <v>0.6209969259688551</v>
+        <v>0.6261486515390992</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.09520194437421</v>
+        <v>17.0307783005875</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07928760448932741</v>
+        <v>0.07902364211217415</v>
       </c>
       <c r="C19">
-        <v>1185.175167637576</v>
+        <v>1176.833005648591</v>
       </c>
       <c r="D19">
-        <v>1421.080167637576</v>
+        <v>1427.403005648591</v>
       </c>
       <c r="E19">
-        <v>-531.895</v>
+        <v>-517.23</v>
       </c>
       <c r="F19">
-        <v>249.305</v>
+        <v>263.97</v>
       </c>
       <c r="G19">
         <v>13.4</v>
@@ -2845,28 +2845,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M19">
-        <v>12.5400415</v>
+        <v>13.277691</v>
       </c>
       <c r="N19">
-        <v>201.0266251666667</v>
+        <v>200.2889756666667</v>
       </c>
       <c r="O19">
-        <v>70.35931880833333</v>
+        <v>70.10114148333332</v>
       </c>
       <c r="P19">
-        <v>130.6673063583333</v>
+        <v>130.1878341833333</v>
       </c>
       <c r="Q19">
-        <v>130.7673063583333</v>
+        <v>130.2878341833333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08883066805943063</v>
+        <v>0.08919334403923677</v>
       </c>
       <c r="T19">
-        <v>0.6261486515390992</v>
+        <v>0.6314260289525198</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.0307783005875</v>
+        <v>16.08462395055486</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07902364211217416</v>
+        <v>0.0787596797350209</v>
       </c>
       <c r="C20">
-        <v>1176.83300564859</v>
+        <v>1168.547359755583</v>
       </c>
       <c r="D20">
-        <v>1427.40300564859</v>
+        <v>1433.782359755583</v>
       </c>
       <c r="E20">
-        <v>-517.23</v>
+        <v>-502.5650000000001</v>
       </c>
       <c r="F20">
-        <v>263.97</v>
+        <v>278.635</v>
       </c>
       <c r="G20">
         <v>13.4</v>
@@ -2927,28 +2927,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M20">
-        <v>13.277691</v>
+        <v>14.0153405</v>
       </c>
       <c r="N20">
-        <v>200.2889756666667</v>
+        <v>199.5513261666667</v>
       </c>
       <c r="O20">
-        <v>70.10114148333332</v>
+        <v>69.84296415833333</v>
       </c>
       <c r="P20">
-        <v>130.1878341833333</v>
+        <v>129.7083620083333</v>
       </c>
       <c r="Q20">
-        <v>130.2878341833333</v>
+        <v>129.8083620083333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08919334403923677</v>
+        <v>0.08956497498150728</v>
       </c>
       <c r="T20">
-        <v>0.6314260289525198</v>
+        <v>0.6368337119810867</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.08462395055486</v>
+        <v>15.2380647952625</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0787596797350209</v>
+        <v>0.07849571735786763</v>
       </c>
       <c r="C21">
-        <v>1168.547359755583</v>
+        <v>1160.318991106032</v>
       </c>
       <c r="D21">
-        <v>1433.782359755583</v>
+        <v>1440.218991106032</v>
       </c>
       <c r="E21">
-        <v>-502.5650000000001</v>
+        <v>-487.9</v>
       </c>
       <c r="F21">
-        <v>278.635</v>
+        <v>293.3</v>
       </c>
       <c r="G21">
         <v>13.4</v>
@@ -3009,28 +3009,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M21">
-        <v>14.0153405</v>
+        <v>14.75299</v>
       </c>
       <c r="N21">
-        <v>199.5513261666667</v>
+        <v>198.8136766666667</v>
       </c>
       <c r="O21">
-        <v>69.84296415833333</v>
+        <v>69.58478683333333</v>
       </c>
       <c r="P21">
-        <v>129.7083620083333</v>
+        <v>129.2288898333333</v>
       </c>
       <c r="Q21">
-        <v>129.8083620083333</v>
+        <v>129.3288898333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08956497498150728</v>
+        <v>0.08994589669733453</v>
       </c>
       <c r="T21">
-        <v>0.6368337119810867</v>
+        <v>0.6423765870853677</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.2380647952625</v>
+        <v>14.47616155549937</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07849571735786763</v>
+        <v>0.07823175498071436</v>
       </c>
       <c r="C22">
-        <v>1160.318991106032</v>
+        <v>1152.148674577024</v>
       </c>
       <c r="D22">
-        <v>1440.218991106032</v>
+        <v>1446.713674577024</v>
       </c>
       <c r="E22">
-        <v>-487.9</v>
+        <v>-473.235</v>
       </c>
       <c r="F22">
-        <v>293.3</v>
+        <v>307.965</v>
       </c>
       <c r="G22">
         <v>13.4</v>
@@ -3091,28 +3091,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M22">
-        <v>14.75299</v>
+        <v>15.4906395</v>
       </c>
       <c r="N22">
-        <v>198.8136766666667</v>
+        <v>198.0760271666667</v>
       </c>
       <c r="O22">
-        <v>69.58478683333333</v>
+        <v>69.32660950833333</v>
       </c>
       <c r="P22">
-        <v>129.2288898333333</v>
+        <v>128.7494176583334</v>
       </c>
       <c r="Q22">
-        <v>129.3288898333333</v>
+        <v>128.8494176583334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08994589669733453</v>
+        <v>0.09033646200090426</v>
       </c>
       <c r="T22">
-        <v>0.6423765870853677</v>
+        <v>0.6480597881416558</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.47616155549937</v>
+        <v>13.78682052904702</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07823175498071436</v>
+        <v>0.07796779260356111</v>
       </c>
       <c r="C23">
-        <v>1152.148674577024</v>
+        <v>1144.037199086231</v>
       </c>
       <c r="D23">
-        <v>1446.713674577024</v>
+        <v>1453.267199086231</v>
       </c>
       <c r="E23">
-        <v>-473.2350000000001</v>
+        <v>-458.5700000000001</v>
       </c>
       <c r="F23">
-        <v>307.965</v>
+        <v>322.63</v>
       </c>
       <c r="G23">
         <v>13.4</v>
@@ -3173,28 +3173,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M23">
-        <v>15.4906395</v>
+        <v>16.228289</v>
       </c>
       <c r="N23">
-        <v>198.0760271666667</v>
+        <v>197.3383776666667</v>
       </c>
       <c r="O23">
-        <v>69.32660950833333</v>
+        <v>69.06843218333333</v>
       </c>
       <c r="P23">
-        <v>128.7494176583334</v>
+        <v>128.2699454833333</v>
       </c>
       <c r="Q23">
-        <v>128.8494176583334</v>
+        <v>128.3699454833333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09033646200090426</v>
+        <v>0.09073704179943731</v>
       </c>
       <c r="T23">
-        <v>0.6480597881416558</v>
+        <v>0.6538887123019513</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.78682052904702</v>
+        <v>13.16014686863579</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07796779260356111</v>
+        <v>0.07792808022640783</v>
       </c>
       <c r="C24">
-        <v>1144.037199086231</v>
+        <v>1130.36329970232</v>
       </c>
       <c r="D24">
-        <v>1453.267199086231</v>
+        <v>1454.25829970232</v>
       </c>
       <c r="E24">
-        <v>-458.5700000000001</v>
+        <v>-443.905</v>
       </c>
       <c r="F24">
-        <v>322.63</v>
+        <v>337.295</v>
       </c>
       <c r="G24">
         <v>13.4</v>
@@ -3255,45 +3255,45 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M24">
-        <v>16.228289</v>
+        <v>17.471881</v>
       </c>
       <c r="N24">
-        <v>197.3383776666667</v>
+        <v>196.0947856666667</v>
       </c>
       <c r="O24">
-        <v>69.06843218333333</v>
+        <v>68.63317498333333</v>
       </c>
       <c r="P24">
-        <v>128.2699454833333</v>
+        <v>127.4616106833333</v>
       </c>
       <c r="Q24">
-        <v>128.3699454833333</v>
+        <v>127.5616106833333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09073704179943731</v>
+        <v>0.09114802626806212</v>
       </c>
       <c r="T24">
-        <v>0.6538887123019513</v>
+        <v>0.6598690370897869</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.16014686863579</v>
+        <v>12.22345016353229</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07792808022640783</v>
+        <v>0.07767386784925456</v>
       </c>
       <c r="C25">
-        <v>1130.36329970232</v>
+        <v>1122.07483452767</v>
       </c>
       <c r="D25">
-        <v>1454.25829970232</v>
+        <v>1460.63483452767</v>
       </c>
       <c r="E25">
-        <v>-443.905</v>
+        <v>-429.24</v>
       </c>
       <c r="F25">
-        <v>337.295</v>
+        <v>351.96</v>
       </c>
       <c r="G25">
         <v>13.4</v>
@@ -3337,28 +3337,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M25">
-        <v>17.471881</v>
+        <v>18.231528</v>
       </c>
       <c r="N25">
-        <v>196.0947856666667</v>
+        <v>195.3351386666667</v>
       </c>
       <c r="O25">
-        <v>68.63317498333333</v>
+        <v>68.36729853333333</v>
       </c>
       <c r="P25">
-        <v>127.4616106833333</v>
+        <v>126.9678401333333</v>
       </c>
       <c r="Q25">
-        <v>127.5616106833333</v>
+        <v>127.0678401333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09114802626806212</v>
+        <v>0.09156982611744022</v>
       </c>
       <c r="T25">
-        <v>0.6598690370897869</v>
+        <v>0.6660067388457236</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.22345016353229</v>
+        <v>11.71413974005178</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07767386784925456</v>
+        <v>0.07741965547210131</v>
       </c>
       <c r="C26">
-        <v>1122.07483452767</v>
+        <v>1113.842534431365</v>
       </c>
       <c r="D26">
-        <v>1460.63483452767</v>
+        <v>1467.067534431365</v>
       </c>
       <c r="E26">
-        <v>-429.2400000000001</v>
+        <v>-414.575</v>
       </c>
       <c r="F26">
-        <v>351.96</v>
+        <v>366.625</v>
       </c>
       <c r="G26">
         <v>13.4</v>
@@ -3419,28 +3419,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M26">
-        <v>18.231528</v>
+        <v>18.991175</v>
       </c>
       <c r="N26">
-        <v>195.3351386666667</v>
+        <v>194.5754916666667</v>
       </c>
       <c r="O26">
-        <v>68.36729853333333</v>
+        <v>68.10142208333333</v>
       </c>
       <c r="P26">
-        <v>126.9678401333333</v>
+        <v>126.4740695833333</v>
       </c>
       <c r="Q26">
-        <v>127.0678401333333</v>
+        <v>126.5740695833333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09156982611744022</v>
+        <v>0.09200287396280174</v>
       </c>
       <c r="T26">
-        <v>0.6660067388457236</v>
+        <v>0.6723081126484852</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.71413974005178</v>
+        <v>11.24557415044971</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07741965547210131</v>
+        <v>0.07716544309494804</v>
       </c>
       <c r="C27">
-        <v>1113.842534431365</v>
+        <v>1105.667144756336</v>
       </c>
       <c r="D27">
-        <v>1467.067534431365</v>
+        <v>1473.557144756336</v>
       </c>
       <c r="E27">
-        <v>-414.575</v>
+        <v>-399.91</v>
       </c>
       <c r="F27">
-        <v>366.625</v>
+        <v>381.29</v>
       </c>
       <c r="G27">
         <v>13.4</v>
@@ -3501,28 +3501,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M27">
-        <v>18.991175</v>
+        <v>19.750822</v>
       </c>
       <c r="N27">
-        <v>194.5754916666667</v>
+        <v>193.8158446666667</v>
       </c>
       <c r="O27">
-        <v>68.10142208333333</v>
+        <v>67.83554563333333</v>
       </c>
       <c r="P27">
-        <v>126.4740695833333</v>
+        <v>125.9802990333333</v>
       </c>
       <c r="Q27">
-        <v>126.5740695833333</v>
+        <v>126.0802990333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09200287396280174</v>
+        <v>0.09244762580398383</v>
       </c>
       <c r="T27">
-        <v>0.6723081126484852</v>
+        <v>0.6787797938513214</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.24557415044971</v>
+        <v>10.8130520677401</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07716544309494804</v>
+        <v>0.07691123071779477</v>
       </c>
       <c r="C28">
-        <v>1105.667144756336</v>
+        <v>1097.549424092286</v>
       </c>
       <c r="D28">
-        <v>1473.557144756336</v>
+        <v>1480.104424092286</v>
       </c>
       <c r="E28">
-        <v>-399.91</v>
+        <v>-385.245</v>
       </c>
       <c r="F28">
-        <v>381.29</v>
+        <v>395.955</v>
       </c>
       <c r="G28">
         <v>13.4</v>
@@ -3583,28 +3583,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M28">
-        <v>19.750822</v>
+        <v>20.510469</v>
       </c>
       <c r="N28">
-        <v>193.8158446666667</v>
+        <v>193.0561976666667</v>
       </c>
       <c r="O28">
-        <v>67.83554563333333</v>
+        <v>67.56966918333333</v>
       </c>
       <c r="P28">
-        <v>125.9802990333333</v>
+        <v>125.4865284833333</v>
       </c>
       <c r="Q28">
-        <v>126.0802990333333</v>
+        <v>125.5865284833333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09244762580398383</v>
+        <v>0.09290456262711612</v>
       </c>
       <c r="T28">
-        <v>0.6787797938513214</v>
+        <v>0.6854287813884818</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.8130520677401</v>
+        <v>10.4125686578238</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07691123071779477</v>
+        <v>0.07665701834064151</v>
       </c>
       <c r="C29">
-        <v>1097.549424092286</v>
+        <v>1089.490144571289</v>
       </c>
       <c r="D29">
-        <v>1480.104424092286</v>
+        <v>1486.710144571289</v>
       </c>
       <c r="E29">
-        <v>-385.245</v>
+        <v>-370.58</v>
       </c>
       <c r="F29">
-        <v>395.955</v>
+        <v>410.6200000000001</v>
       </c>
       <c r="G29">
         <v>13.4</v>
@@ -3665,28 +3665,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M29">
-        <v>20.510469</v>
+        <v>21.270116</v>
       </c>
       <c r="N29">
-        <v>193.0561976666667</v>
+        <v>192.2965506666667</v>
       </c>
       <c r="O29">
-        <v>67.56966918333333</v>
+        <v>67.30379273333332</v>
       </c>
       <c r="P29">
-        <v>125.4865284833333</v>
+        <v>124.9927579333333</v>
       </c>
       <c r="Q29">
-        <v>125.5865284833333</v>
+        <v>125.0927579333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09290456262711612</v>
+        <v>0.09337419213977988</v>
       </c>
       <c r="T29">
-        <v>0.6854287813884818</v>
+        <v>0.6922624630238968</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.4125686578238</v>
+        <v>10.04069120575866</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07665701834064151</v>
+        <v>0.07672325596348824</v>
       </c>
       <c r="C30">
-        <v>1089.490144571289</v>
+        <v>1073.098283311097</v>
       </c>
       <c r="D30">
-        <v>1486.710144571289</v>
+        <v>1484.983283311097</v>
       </c>
       <c r="E30">
-        <v>-370.58</v>
+        <v>-355.915</v>
       </c>
       <c r="F30">
-        <v>410.6200000000001</v>
+        <v>425.285</v>
       </c>
       <c r="G30">
         <v>13.4</v>
@@ -3747,45 +3747,45 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M30">
-        <v>21.270116</v>
+        <v>22.7527475</v>
       </c>
       <c r="N30">
-        <v>192.2965506666667</v>
+        <v>190.8139191666667</v>
       </c>
       <c r="O30">
-        <v>67.30379273333332</v>
+        <v>66.78487170833333</v>
       </c>
       <c r="P30">
-        <v>124.9927579333333</v>
+        <v>124.0290474583333</v>
       </c>
       <c r="Q30">
-        <v>125.0927579333333</v>
+        <v>124.1290474583333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09337419213977988</v>
+        <v>0.09385705065280034</v>
       </c>
       <c r="T30">
-        <v>0.6922624630238968</v>
+        <v>0.6992886427335487</v>
       </c>
       <c r="U30">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.35</v>
       </c>
       <c r="W30">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>10.04069120575866</v>
+        <v>9.386412197764979</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07672325596348824</v>
+        <v>0.07648009358633497</v>
       </c>
       <c r="C31">
-        <v>1073.098283311097</v>
+        <v>1064.79244934203</v>
       </c>
       <c r="D31">
-        <v>1484.983283311097</v>
+        <v>1491.34244934203</v>
       </c>
       <c r="E31">
-        <v>-355.9150000000001</v>
+        <v>-341.2500000000001</v>
       </c>
       <c r="F31">
-        <v>425.285</v>
+        <v>439.95</v>
       </c>
       <c r="G31">
         <v>13.4</v>
@@ -3829,28 +3829,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M31">
-        <v>22.7527475</v>
+        <v>23.537325</v>
       </c>
       <c r="N31">
-        <v>190.8139191666667</v>
+        <v>190.0293416666667</v>
       </c>
       <c r="O31">
-        <v>66.78487170833333</v>
+        <v>66.51026958333333</v>
       </c>
       <c r="P31">
-        <v>124.0290474583333</v>
+        <v>123.5190720833333</v>
       </c>
       <c r="Q31">
-        <v>124.1290474583333</v>
+        <v>123.6190720833333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09385705065280034</v>
+        <v>0.09435370512333567</v>
       </c>
       <c r="T31">
-        <v>0.6992886427335487</v>
+        <v>0.7065155704349051</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.386412197764981</v>
+        <v>9.073531791172813</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07648009358633497</v>
+        <v>0.07623693120918171</v>
       </c>
       <c r="C32">
-        <v>1064.79244934203</v>
+        <v>1056.541313510423</v>
       </c>
       <c r="D32">
-        <v>1491.34244934203</v>
+        <v>1497.756313510423</v>
       </c>
       <c r="E32">
-        <v>-341.2500000000001</v>
+        <v>-326.585</v>
       </c>
       <c r="F32">
-        <v>439.95</v>
+        <v>454.615</v>
       </c>
       <c r="G32">
         <v>13.4</v>
@@ -3911,28 +3911,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M32">
-        <v>23.537325</v>
+        <v>24.3219025</v>
       </c>
       <c r="N32">
-        <v>190.0293416666667</v>
+        <v>189.2447641666667</v>
       </c>
       <c r="O32">
-        <v>66.51026958333333</v>
+        <v>66.23566745833332</v>
       </c>
       <c r="P32">
-        <v>123.5190720833333</v>
+        <v>123.0090967083333</v>
       </c>
       <c r="Q32">
-        <v>123.6190720833333</v>
+        <v>123.1090967083333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09435370512333567</v>
+        <v>0.09486475537562566</v>
       </c>
       <c r="T32">
-        <v>0.7065155704349051</v>
+        <v>0.7139519743015182</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.073531791172813</v>
+        <v>8.780837217264015</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07623693120918171</v>
+        <v>0.07599376883202844</v>
       </c>
       <c r="C33">
-        <v>1056.541313510423</v>
+        <v>1048.345584590611</v>
       </c>
       <c r="D33">
-        <v>1497.756313510423</v>
+        <v>1504.225584590611</v>
       </c>
       <c r="E33">
-        <v>-326.585</v>
+        <v>-311.92</v>
       </c>
       <c r="F33">
-        <v>454.615</v>
+        <v>469.28</v>
       </c>
       <c r="G33">
         <v>13.4</v>
@@ -3993,28 +3993,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M33">
-        <v>24.3219025</v>
+        <v>25.10648</v>
       </c>
       <c r="N33">
-        <v>189.2447641666667</v>
+        <v>188.4601866666667</v>
       </c>
       <c r="O33">
-        <v>66.23566745833332</v>
+        <v>65.96106533333332</v>
       </c>
       <c r="P33">
-        <v>123.0090967083333</v>
+        <v>122.4991213333333</v>
       </c>
       <c r="Q33">
-        <v>123.1090967083333</v>
+        <v>122.5991213333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09486475537562566</v>
+        <v>0.09539083651768888</v>
       </c>
       <c r="T33">
-        <v>0.7139519743015182</v>
+        <v>0.7216070959289139</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.780837217264015</v>
+        <v>8.506436054224512</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07599376883202844</v>
+        <v>0.07575060645487516</v>
       </c>
       <c r="C34">
-        <v>1048.345584590611</v>
+        <v>1040.205983655712</v>
       </c>
       <c r="D34">
-        <v>1504.225584590611</v>
+        <v>1510.750983655712</v>
       </c>
       <c r="E34">
-        <v>-311.92</v>
+        <v>-297.255</v>
       </c>
       <c r="F34">
-        <v>469.28</v>
+        <v>483.9450000000001</v>
       </c>
       <c r="G34">
         <v>13.4</v>
@@ -4075,28 +4075,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M34">
-        <v>25.10648</v>
+        <v>25.8910575</v>
       </c>
       <c r="N34">
-        <v>188.4601866666667</v>
+        <v>187.6756091666667</v>
       </c>
       <c r="O34">
-        <v>65.96106533333332</v>
+        <v>65.68646320833334</v>
       </c>
       <c r="P34">
-        <v>122.4991213333333</v>
+        <v>121.9891459583333</v>
       </c>
       <c r="Q34">
-        <v>122.5991213333333</v>
+        <v>122.0891459583333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09539083651768888</v>
+        <v>0.09593262157444056</v>
       </c>
       <c r="T34">
-        <v>0.7216070959289139</v>
+        <v>0.7294907286496648</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.506436054224512</v>
+        <v>8.248665264702559</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07575060645487516</v>
+        <v>0.07550744407772191</v>
       </c>
       <c r="C35">
-        <v>1040.205983655712</v>
+        <v>1032.123244345549</v>
       </c>
       <c r="D35">
-        <v>1510.750983655712</v>
+        <v>1517.333244345549</v>
       </c>
       <c r="E35">
-        <v>-297.255</v>
+        <v>-282.59</v>
       </c>
       <c r="F35">
-        <v>483.9450000000001</v>
+        <v>498.61</v>
       </c>
       <c r="G35">
         <v>13.4</v>
@@ -4157,28 +4157,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M35">
-        <v>25.8910575</v>
+        <v>26.675635</v>
       </c>
       <c r="N35">
-        <v>187.6756091666667</v>
+        <v>186.8910316666667</v>
       </c>
       <c r="O35">
-        <v>65.68646320833334</v>
+        <v>65.41186108333333</v>
       </c>
       <c r="P35">
-        <v>121.9891459583333</v>
+        <v>121.4791705833333</v>
       </c>
       <c r="Q35">
-        <v>122.0891459583333</v>
+        <v>121.5791705833333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09593262157444056</v>
+        <v>0.09649082436018472</v>
       </c>
       <c r="T35">
-        <v>0.7294907286496648</v>
+        <v>0.7376132593316507</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.248665264702559</v>
+        <v>8.006057462799543</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07550744407772191</v>
+        <v>0.07526428170056865</v>
       </c>
       <c r="C36">
-        <v>1032.123244345549</v>
+        <v>1024.098113141614</v>
       </c>
       <c r="D36">
-        <v>1517.333244345549</v>
+        <v>1523.973113141614</v>
       </c>
       <c r="E36">
-        <v>-282.59</v>
+        <v>-267.925</v>
       </c>
       <c r="F36">
-        <v>498.61</v>
+        <v>513.2750000000001</v>
       </c>
       <c r="G36">
         <v>13.4</v>
@@ -4239,28 +4239,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M36">
-        <v>26.675635</v>
+        <v>27.4602125</v>
       </c>
       <c r="N36">
-        <v>186.8910316666667</v>
+        <v>186.1064541666667</v>
       </c>
       <c r="O36">
-        <v>65.41186108333333</v>
+        <v>65.13725895833332</v>
       </c>
       <c r="P36">
-        <v>121.4791705833333</v>
+        <v>120.9691952083333</v>
       </c>
       <c r="Q36">
-        <v>121.5791705833333</v>
+        <v>121.0691952083333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09649082436018472</v>
+        <v>0.09706620261625945</v>
       </c>
       <c r="T36">
-        <v>0.7376132593316507</v>
+        <v>0.7459857140346206</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.006057462799543</v>
+        <v>7.777312963862411</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07526428170056865</v>
+        <v>0.07520831932341537</v>
       </c>
       <c r="C37">
-        <v>1024.098113141614</v>
+        <v>1010.969473905019</v>
       </c>
       <c r="D37">
-        <v>1523.973113141614</v>
+        <v>1525.509473905019</v>
       </c>
       <c r="E37">
-        <v>-267.925</v>
+        <v>-253.26</v>
       </c>
       <c r="F37">
-        <v>513.2750000000001</v>
+        <v>527.9400000000001</v>
       </c>
       <c r="G37">
         <v>13.4</v>
@@ -4321,45 +4321,45 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M37">
-        <v>27.4602125</v>
+        <v>28.667142</v>
       </c>
       <c r="N37">
-        <v>186.1064541666667</v>
+        <v>184.8995246666667</v>
       </c>
       <c r="O37">
-        <v>65.13725895833332</v>
+        <v>64.71483363333333</v>
       </c>
       <c r="P37">
-        <v>120.9691952083333</v>
+        <v>120.1846910333333</v>
       </c>
       <c r="Q37">
-        <v>121.0691952083333</v>
+        <v>120.2846910333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09706620261625945</v>
+        <v>0.09765956144283654</v>
       </c>
       <c r="T37">
-        <v>0.7459857140346206</v>
+        <v>0.7546198079470583</v>
       </c>
       <c r="U37">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.35</v>
       </c>
       <c r="W37">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>7.777312963862411</v>
+        <v>7.449876470652939</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07520831932341539</v>
+        <v>0.07497035694626213</v>
       </c>
       <c r="C38">
-        <v>1010.969473905019</v>
+        <v>1002.872103773591</v>
       </c>
       <c r="D38">
-        <v>1525.509473905018</v>
+        <v>1532.077103773591</v>
       </c>
       <c r="E38">
-        <v>-253.2600000000001</v>
+        <v>-238.595</v>
       </c>
       <c r="F38">
-        <v>527.9399999999999</v>
+        <v>542.605</v>
       </c>
       <c r="G38">
         <v>13.4</v>
@@ -4403,28 +4403,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M38">
-        <v>28.667142</v>
+        <v>29.4634515</v>
       </c>
       <c r="N38">
-        <v>184.8995246666667</v>
+        <v>184.1032151666667</v>
       </c>
       <c r="O38">
-        <v>64.71483363333333</v>
+        <v>64.43612530833333</v>
       </c>
       <c r="P38">
-        <v>120.1846910333333</v>
+        <v>119.6670898583333</v>
       </c>
       <c r="Q38">
-        <v>120.2846910333333</v>
+        <v>119.7670898583333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09765956144283654</v>
+        <v>0.09827175705755892</v>
       </c>
       <c r="T38">
-        <v>0.7546198079470583</v>
+        <v>0.7635280000789384</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.44987647065294</v>
+        <v>7.24852845793259</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07497035694626213</v>
+        <v>0.07473239456910885</v>
       </c>
       <c r="C39">
-        <v>1002.872103773591</v>
+        <v>994.831528130064</v>
       </c>
       <c r="D39">
-        <v>1532.077103773591</v>
+        <v>1538.701528130064</v>
       </c>
       <c r="E39">
-        <v>-238.595</v>
+        <v>-223.9300000000001</v>
       </c>
       <c r="F39">
-        <v>542.605</v>
+        <v>557.27</v>
       </c>
       <c r="G39">
         <v>13.4</v>
@@ -4485,28 +4485,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M39">
-        <v>29.4634515</v>
+        <v>30.259761</v>
       </c>
       <c r="N39">
-        <v>184.1032151666667</v>
+        <v>183.3069056666667</v>
       </c>
       <c r="O39">
-        <v>64.43612530833333</v>
+        <v>64.15741698333333</v>
       </c>
       <c r="P39">
-        <v>119.6670898583333</v>
+        <v>119.1494886833333</v>
       </c>
       <c r="Q39">
-        <v>119.7670898583333</v>
+        <v>119.2494886833333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09827175705755892</v>
+        <v>0.0989037009179175</v>
       </c>
       <c r="T39">
-        <v>0.7635280000789384</v>
+        <v>0.7727235532473309</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.24852845793259</v>
+        <v>7.057777709039628</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07473239456910885</v>
+        <v>0.07449443219195559</v>
       </c>
       <c r="C40">
-        <v>994.831528130064</v>
+        <v>986.8484868809447</v>
       </c>
       <c r="D40">
-        <v>1538.701528130064</v>
+        <v>1545.383486880945</v>
       </c>
       <c r="E40">
-        <v>-223.9300000000001</v>
+        <v>-209.265</v>
       </c>
       <c r="F40">
-        <v>557.27</v>
+        <v>571.9350000000001</v>
       </c>
       <c r="G40">
         <v>13.4</v>
@@ -4567,28 +4567,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M40">
-        <v>30.259761</v>
+        <v>31.0560705</v>
       </c>
       <c r="N40">
-        <v>183.3069056666667</v>
+        <v>182.5105961666667</v>
       </c>
       <c r="O40">
-        <v>64.15741698333333</v>
+        <v>63.87870865833332</v>
       </c>
       <c r="P40">
-        <v>119.1494886833333</v>
+        <v>118.6318875083333</v>
       </c>
       <c r="Q40">
-        <v>119.2494886833333</v>
+        <v>118.7318875083333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0989037009179175</v>
+        <v>0.09955636424910752</v>
       </c>
       <c r="T40">
-        <v>0.7727235532473309</v>
+        <v>0.7822205999622281</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.057777709039628</v>
+        <v>6.876809049833482</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07449443219195559</v>
+        <v>0.07425646981480231</v>
       </c>
       <c r="C41">
-        <v>986.8484868809447</v>
+        <v>978.9237328412595</v>
       </c>
       <c r="D41">
-        <v>1545.383486880945</v>
+        <v>1552.123732841259</v>
       </c>
       <c r="E41">
-        <v>-209.265</v>
+        <v>-194.6</v>
       </c>
       <c r="F41">
-        <v>571.9350000000001</v>
+        <v>586.6</v>
       </c>
       <c r="G41">
         <v>13.4</v>
@@ -4649,28 +4649,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M41">
-        <v>31.0560705</v>
+        <v>31.85238</v>
       </c>
       <c r="N41">
-        <v>182.5105961666667</v>
+        <v>181.7142866666667</v>
       </c>
       <c r="O41">
-        <v>63.87870865833332</v>
+        <v>63.60000033333333</v>
       </c>
       <c r="P41">
-        <v>118.6318875083333</v>
+        <v>118.1142863333333</v>
       </c>
       <c r="Q41">
-        <v>118.7318875083333</v>
+        <v>118.2142863333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09955636424910752</v>
+        <v>0.1002307830246705</v>
       </c>
       <c r="T41">
-        <v>0.7822205999622281</v>
+        <v>0.792034214900955</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.876809049833482</v>
+        <v>6.704888823587646</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07425646981480231</v>
+        <v>0.07401850743764905</v>
       </c>
       <c r="C42">
-        <v>978.9237328412595</v>
+        <v>971.0580320172867</v>
       </c>
       <c r="D42">
-        <v>1552.123732841259</v>
+        <v>1558.923032017287</v>
       </c>
       <c r="E42">
-        <v>-194.6</v>
+        <v>-179.9349999999999</v>
       </c>
       <c r="F42">
-        <v>586.6</v>
+        <v>601.2650000000001</v>
       </c>
       <c r="G42">
         <v>13.4</v>
@@ -4731,28 +4731,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M42">
-        <v>31.85238</v>
+        <v>32.6486895</v>
       </c>
       <c r="N42">
-        <v>181.7142866666667</v>
+        <v>180.9179771666667</v>
       </c>
       <c r="O42">
-        <v>63.60000033333333</v>
+        <v>63.32129200833333</v>
       </c>
       <c r="P42">
-        <v>118.1142863333333</v>
+        <v>117.5966851583333</v>
       </c>
       <c r="Q42">
-        <v>118.2142863333333</v>
+        <v>117.6966851583333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1002307830246705</v>
+        <v>0.1009280634536425</v>
       </c>
       <c r="T42">
-        <v>0.792034214900955</v>
+        <v>0.8021804947528594</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.704888823587646</v>
+        <v>6.541354949841605</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07401850743764905</v>
+        <v>0.07378054506049579</v>
       </c>
       <c r="C43">
-        <v>971.0580320172867</v>
+        <v>963.2521638967619</v>
       </c>
       <c r="D43">
-        <v>1558.923032017287</v>
+        <v>1565.782163896762</v>
       </c>
       <c r="E43">
-        <v>-179.9349999999999</v>
+        <v>-165.27</v>
       </c>
       <c r="F43">
-        <v>601.2650000000001</v>
+        <v>615.9300000000001</v>
       </c>
       <c r="G43">
         <v>13.4</v>
@@ -4813,28 +4813,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M43">
-        <v>32.6486895</v>
+        <v>33.444999</v>
       </c>
       <c r="N43">
-        <v>180.9179771666667</v>
+        <v>180.1216676666667</v>
       </c>
       <c r="O43">
-        <v>63.32129200833333</v>
+        <v>63.04258368333333</v>
       </c>
       <c r="P43">
-        <v>117.5966851583333</v>
+        <v>117.0790839833333</v>
       </c>
       <c r="Q43">
-        <v>117.6966851583333</v>
+        <v>117.1790839833333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1009280634536425</v>
+        <v>0.1016493880353376</v>
       </c>
       <c r="T43">
-        <v>0.8021804947528594</v>
+        <v>0.8126766463237948</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.541354949841605</v>
+        <v>6.385608403416805</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07378054506049579</v>
+        <v>0.07354258268334253</v>
       </c>
       <c r="C44">
-        <v>963.252163896762</v>
+        <v>955.5069217467733</v>
       </c>
       <c r="D44">
-        <v>1565.782163896762</v>
+        <v>1572.701921746773</v>
       </c>
       <c r="E44">
-        <v>-165.2700000000001</v>
+        <v>-150.605</v>
       </c>
       <c r="F44">
-        <v>615.9299999999999</v>
+        <v>630.595</v>
       </c>
       <c r="G44">
         <v>13.4</v>
@@ -4895,28 +4895,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M44">
-        <v>33.444999</v>
+        <v>34.2413085</v>
       </c>
       <c r="N44">
-        <v>180.1216676666667</v>
+        <v>179.3253581666667</v>
       </c>
       <c r="O44">
-        <v>63.04258368333333</v>
+        <v>62.76387535833333</v>
       </c>
       <c r="P44">
-        <v>117.0790839833333</v>
+        <v>116.5614828083333</v>
       </c>
       <c r="Q44">
-        <v>117.1790839833333</v>
+        <v>116.6614828083333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1016493880353376</v>
+        <v>0.1023960222514781</v>
       </c>
       <c r="T44">
-        <v>0.8126766463237948</v>
+        <v>0.823541083914763</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.385608403416806</v>
+        <v>6.237105882407112</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07354258268334253</v>
+        <v>0.07359062030618926</v>
       </c>
       <c r="C45">
-        <v>955.5069217467733</v>
+        <v>939.4401028704656</v>
       </c>
       <c r="D45">
-        <v>1572.701921746773</v>
+        <v>1571.300102870465</v>
       </c>
       <c r="E45">
-        <v>-150.605</v>
+        <v>-135.9400000000001</v>
       </c>
       <c r="F45">
-        <v>630.595</v>
+        <v>645.26</v>
       </c>
       <c r="G45">
         <v>13.4</v>
@@ -4977,45 +4977,45 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M45">
-        <v>34.2413085</v>
+        <v>35.682878</v>
       </c>
       <c r="N45">
-        <v>179.3253581666667</v>
+        <v>177.8837886666666</v>
       </c>
       <c r="O45">
-        <v>62.76387535833333</v>
+        <v>62.25932603333332</v>
       </c>
       <c r="P45">
-        <v>116.5614828083333</v>
+        <v>115.6244626333333</v>
       </c>
       <c r="Q45">
-        <v>116.6614828083333</v>
+        <v>115.7244626333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1023960222514781</v>
+        <v>0.103169321975338</v>
       </c>
       <c r="T45">
-        <v>0.823541083914763</v>
+        <v>0.8347935371339801</v>
       </c>
       <c r="U45">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.35</v>
       </c>
       <c r="W45">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>6.237105882407112</v>
+        <v>5.985130085826222</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07359062030618926</v>
+        <v>0.073359157929036</v>
       </c>
       <c r="C46">
-        <v>939.4401028704656</v>
+        <v>931.5526532918258</v>
       </c>
       <c r="D46">
-        <v>1571.300102870465</v>
+        <v>1578.077653291826</v>
       </c>
       <c r="E46">
-        <v>-135.9400000000001</v>
+        <v>-121.275</v>
       </c>
       <c r="F46">
-        <v>645.26</v>
+        <v>659.9250000000001</v>
       </c>
       <c r="G46">
         <v>13.4</v>
@@ -5059,28 +5059,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M46">
-        <v>35.682878</v>
+        <v>36.4938525</v>
       </c>
       <c r="N46">
-        <v>177.8837886666666</v>
+        <v>177.0728141666667</v>
       </c>
       <c r="O46">
-        <v>62.25932603333332</v>
+        <v>61.97548495833333</v>
       </c>
       <c r="P46">
-        <v>115.6244626333333</v>
+        <v>115.0973292083333</v>
       </c>
       <c r="Q46">
-        <v>115.7244626333333</v>
+        <v>115.1973292083333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.103169321975338</v>
+        <v>0.1039707416891563</v>
       </c>
       <c r="T46">
-        <v>0.8347935371339801</v>
+        <v>0.8464551704702595</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.985130085826222</v>
+        <v>5.852127195030085</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.073359157929036</v>
+        <v>0.07312769555188274</v>
       </c>
       <c r="C47">
-        <v>931.5526532918258</v>
+        <v>923.7239247455437</v>
       </c>
       <c r="D47">
-        <v>1578.077653291826</v>
+        <v>1584.913924745544</v>
       </c>
       <c r="E47">
-        <v>-121.275</v>
+        <v>-106.61</v>
       </c>
       <c r="F47">
-        <v>659.9250000000001</v>
+        <v>674.59</v>
       </c>
       <c r="G47">
         <v>13.4</v>
@@ -5141,28 +5141,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M47">
-        <v>36.4938525</v>
+        <v>37.304827</v>
       </c>
       <c r="N47">
-        <v>177.0728141666667</v>
+        <v>176.2618396666667</v>
       </c>
       <c r="O47">
-        <v>61.97548495833333</v>
+        <v>61.69164388333333</v>
       </c>
       <c r="P47">
-        <v>115.0973292083333</v>
+        <v>114.5701957833333</v>
       </c>
       <c r="Q47">
-        <v>115.1973292083333</v>
+        <v>114.6701957833333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1039707416891563</v>
+        <v>0.1048018436145977</v>
       </c>
       <c r="T47">
-        <v>0.8464551704702595</v>
+        <v>0.8585487161523273</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.852127195030085</v>
+        <v>5.724907038616387</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07312769555188274</v>
+        <v>0.07289623317472947</v>
       </c>
       <c r="C48">
-        <v>923.7239247455437</v>
+        <v>915.9546836948558</v>
       </c>
       <c r="D48">
-        <v>1584.913924745544</v>
+        <v>1591.809683694856</v>
       </c>
       <c r="E48">
-        <v>-106.61</v>
+        <v>-91.94500000000005</v>
       </c>
       <c r="F48">
-        <v>674.59</v>
+        <v>689.255</v>
       </c>
       <c r="G48">
         <v>13.4</v>
@@ -5223,28 +5223,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M48">
-        <v>37.304827</v>
+        <v>38.1158015</v>
       </c>
       <c r="N48">
-        <v>176.2618396666667</v>
+        <v>175.4508651666667</v>
       </c>
       <c r="O48">
-        <v>61.69164388333333</v>
+        <v>61.40780280833333</v>
       </c>
       <c r="P48">
-        <v>114.5701957833333</v>
+        <v>114.0430623583333</v>
       </c>
       <c r="Q48">
-        <v>114.6701957833333</v>
+        <v>114.1430623583333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1048018436145977</v>
+        <v>0.1056643078768481</v>
       </c>
       <c r="T48">
-        <v>0.8585487161523273</v>
+        <v>0.8710986220488126</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.724907038616387</v>
+        <v>5.603100505879868</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07289623317472947</v>
+        <v>0.0726647707975762</v>
       </c>
       <c r="C49">
-        <v>915.9546836948558</v>
+        <v>908.2457100004219</v>
       </c>
       <c r="D49">
-        <v>1591.809683694856</v>
+        <v>1598.765710000422</v>
       </c>
       <c r="E49">
-        <v>-91.94500000000005</v>
+        <v>-77.27999999999997</v>
       </c>
       <c r="F49">
-        <v>689.255</v>
+        <v>703.9200000000001</v>
       </c>
       <c r="G49">
         <v>13.4</v>
@@ -5305,28 +5305,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M49">
-        <v>38.1158015</v>
+        <v>38.926776</v>
       </c>
       <c r="N49">
-        <v>175.4508651666667</v>
+        <v>174.6398906666666</v>
       </c>
       <c r="O49">
-        <v>61.40780280833333</v>
+        <v>61.12396173333332</v>
       </c>
       <c r="P49">
-        <v>114.0430623583333</v>
+        <v>113.5159289333333</v>
       </c>
       <c r="Q49">
-        <v>114.1430623583333</v>
+        <v>113.6159289333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1056643078768481</v>
+        <v>0.1065599438414927</v>
       </c>
       <c r="T49">
-        <v>0.8710986220488126</v>
+        <v>0.8841312166336244</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.603100505879868</v>
+        <v>5.486369245340704</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0726647707975762</v>
+        <v>0.07243330842042293</v>
       </c>
       <c r="C50">
-        <v>908.245710000422</v>
+        <v>900.5977972143414</v>
       </c>
       <c r="D50">
-        <v>1598.765710000422</v>
+        <v>1605.782797214341</v>
       </c>
       <c r="E50">
-        <v>-77.28000000000009</v>
+        <v>-62.61500000000001</v>
       </c>
       <c r="F50">
-        <v>703.92</v>
+        <v>718.585</v>
       </c>
       <c r="G50">
         <v>13.4</v>
@@ -5387,28 +5387,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M50">
-        <v>38.926776</v>
+        <v>39.7377505</v>
       </c>
       <c r="N50">
-        <v>174.6398906666667</v>
+        <v>173.8289161666667</v>
       </c>
       <c r="O50">
-        <v>61.12396173333333</v>
+        <v>60.84012065833333</v>
       </c>
       <c r="P50">
-        <v>113.5159289333333</v>
+        <v>112.9887955083333</v>
       </c>
       <c r="Q50">
-        <v>113.6159289333333</v>
+        <v>113.0887955083333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1065599438414927</v>
+        <v>0.107490702785143</v>
       </c>
       <c r="T50">
-        <v>0.8841312166336244</v>
+        <v>0.8976748933590168</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.486369245340706</v>
+        <v>5.374402526048037</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07243330842042293</v>
+        <v>0.07220184604326967</v>
       </c>
       <c r="C51">
-        <v>900.5977972143414</v>
+        <v>893.0117528819392</v>
       </c>
       <c r="D51">
-        <v>1605.782797214341</v>
+        <v>1612.861752881939</v>
       </c>
       <c r="E51">
-        <v>-62.61500000000001</v>
+        <v>-47.95000000000005</v>
       </c>
       <c r="F51">
-        <v>718.585</v>
+        <v>733.25</v>
       </c>
       <c r="G51">
         <v>13.4</v>
@@ -5469,28 +5469,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M51">
-        <v>39.7377505</v>
+        <v>40.548725</v>
       </c>
       <c r="N51">
-        <v>173.8289161666667</v>
+        <v>173.0179416666667</v>
       </c>
       <c r="O51">
-        <v>60.84012065833333</v>
+        <v>60.55627958333333</v>
       </c>
       <c r="P51">
-        <v>112.9887955083333</v>
+        <v>112.4616620833334</v>
       </c>
       <c r="Q51">
-        <v>113.0887955083333</v>
+        <v>112.5616620833333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.107490702785143</v>
+        <v>0.1084586920865393</v>
       </c>
       <c r="T51">
-        <v>0.8976748933590168</v>
+        <v>0.911760317153425</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.374402526048037</v>
+        <v>5.266914475527076</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07220184604326967</v>
+        <v>0.0719703836661164</v>
       </c>
       <c r="C52">
-        <v>893.0117528819392</v>
+        <v>885.4883988515694</v>
       </c>
       <c r="D52">
-        <v>1612.861752881939</v>
+        <v>1620.003398851569</v>
       </c>
       <c r="E52">
-        <v>-47.95000000000005</v>
+        <v>-33.28500000000008</v>
       </c>
       <c r="F52">
-        <v>733.25</v>
+        <v>747.915</v>
       </c>
       <c r="G52">
         <v>13.4</v>
@@ -5551,28 +5551,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M52">
-        <v>40.548725</v>
+        <v>41.3596995</v>
       </c>
       <c r="N52">
-        <v>173.0179416666667</v>
+        <v>172.2069671666667</v>
       </c>
       <c r="O52">
-        <v>60.55627958333333</v>
+        <v>60.27243850833332</v>
       </c>
       <c r="P52">
-        <v>112.4616620833334</v>
+        <v>111.9345286583333</v>
       </c>
       <c r="Q52">
-        <v>112.5616620833333</v>
+        <v>112.0345286583333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1084586920865393</v>
+        <v>0.1094661911553396</v>
       </c>
       <c r="T52">
-        <v>0.911760317153425</v>
+        <v>0.9264206562047479</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.266914475527076</v>
+        <v>5.163641642673604</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0719703836661164</v>
+        <v>0.07173892128896314</v>
       </c>
       <c r="C53">
-        <v>885.4883988515694</v>
+        <v>878.0285715926904</v>
       </c>
       <c r="D53">
-        <v>1620.003398851569</v>
+        <v>1627.20857159269</v>
       </c>
       <c r="E53">
-        <v>-33.28500000000008</v>
+        <v>-18.62</v>
       </c>
       <c r="F53">
-        <v>747.915</v>
+        <v>762.58</v>
       </c>
       <c r="G53">
         <v>13.4</v>
@@ -5633,28 +5633,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M53">
-        <v>41.3596995</v>
+        <v>42.17067400000001</v>
       </c>
       <c r="N53">
-        <v>172.2069671666667</v>
+        <v>171.3959926666666</v>
       </c>
       <c r="O53">
-        <v>60.27243850833332</v>
+        <v>59.98859743333332</v>
       </c>
       <c r="P53">
-        <v>111.9345286583333</v>
+        <v>111.4073952333333</v>
       </c>
       <c r="Q53">
-        <v>112.0345286583333</v>
+        <v>111.5073952333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1094661911553396</v>
+        <v>0.1105156693520065</v>
       </c>
       <c r="T53">
-        <v>0.9264206562047479</v>
+        <v>0.9416918427165426</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.163641642673604</v>
+        <v>5.064340841852958</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07173892128896314</v>
+        <v>0.07150745891180987</v>
       </c>
       <c r="C54">
-        <v>878.0285715926904</v>
+        <v>870.6331225224645</v>
       </c>
       <c r="D54">
-        <v>1627.20857159269</v>
+        <v>1634.478122522464</v>
       </c>
       <c r="E54">
-        <v>-18.62</v>
+        <v>-3.955000000000041</v>
       </c>
       <c r="F54">
-        <v>762.58</v>
+        <v>777.245</v>
       </c>
       <c r="G54">
         <v>13.4</v>
@@ -5715,28 +5715,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M54">
-        <v>42.17067400000001</v>
+        <v>42.9816485</v>
       </c>
       <c r="N54">
-        <v>171.3959926666666</v>
+        <v>170.5850181666667</v>
       </c>
       <c r="O54">
-        <v>59.98859743333332</v>
+        <v>59.70475635833333</v>
       </c>
       <c r="P54">
-        <v>111.4073952333333</v>
+        <v>110.8802618083333</v>
       </c>
       <c r="Q54">
-        <v>111.5073952333333</v>
+        <v>110.9802618083333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1105156693520065</v>
+        <v>0.1116098061953402</v>
       </c>
       <c r="T54">
-        <v>0.9416918427165426</v>
+        <v>0.9576128669522435</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.064340841852958</v>
+        <v>4.96878724106328</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07150745891180987</v>
+        <v>0.0712759965346566</v>
       </c>
       <c r="C55">
-        <v>870.6331225224645</v>
+        <v>863.302918341147</v>
       </c>
       <c r="D55">
-        <v>1634.478122522464</v>
+        <v>1641.812918341147</v>
       </c>
       <c r="E55">
-        <v>-3.955000000000041</v>
+        <v>10.71000000000004</v>
       </c>
       <c r="F55">
-        <v>777.245</v>
+        <v>791.9100000000001</v>
       </c>
       <c r="G55">
         <v>13.4</v>
@@ -5797,28 +5797,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M55">
-        <v>42.9816485</v>
+        <v>43.79262300000001</v>
       </c>
       <c r="N55">
-        <v>170.5850181666667</v>
+        <v>169.7740436666667</v>
       </c>
       <c r="O55">
-        <v>59.70475635833333</v>
+        <v>59.42091528333333</v>
       </c>
       <c r="P55">
-        <v>110.8802618083333</v>
+        <v>110.3531283833333</v>
       </c>
       <c r="Q55">
-        <v>110.9802618083333</v>
+        <v>110.4531283833333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1116098061953402</v>
+        <v>0.1127515142057752</v>
       </c>
       <c r="T55">
-        <v>0.9576128669522435</v>
+        <v>0.9742261096329746</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.96878724106328</v>
+        <v>4.87677266252507</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0712759965346566</v>
+        <v>0.07104453415750334</v>
       </c>
       <c r="C56">
-        <v>863.302918341147</v>
+        <v>856.0388413765518</v>
       </c>
       <c r="D56">
-        <v>1641.812918341147</v>
+        <v>1649.213841376552</v>
       </c>
       <c r="E56">
-        <v>10.71000000000004</v>
+        <v>25.375</v>
       </c>
       <c r="F56">
-        <v>791.9100000000001</v>
+        <v>806.575</v>
       </c>
       <c r="G56">
         <v>13.4</v>
@@ -5879,28 +5879,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M56">
-        <v>43.79262300000001</v>
+        <v>44.60359750000001</v>
       </c>
       <c r="N56">
-        <v>169.7740436666667</v>
+        <v>168.9630691666667</v>
       </c>
       <c r="O56">
-        <v>59.42091528333333</v>
+        <v>59.13707420833332</v>
       </c>
       <c r="P56">
-        <v>110.3531283833333</v>
+        <v>109.8259949583333</v>
       </c>
       <c r="Q56">
-        <v>110.4531283833333</v>
+        <v>109.9259949583333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1127515142057752</v>
+        <v>0.1139439647944519</v>
       </c>
       <c r="T56">
-        <v>0.9742261096329746</v>
+        <v>0.9915777186550718</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.87677266252507</v>
+        <v>4.788104068660978</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07104453415750334</v>
+        <v>0.07081307178035008</v>
       </c>
       <c r="C57">
-        <v>856.0388413765518</v>
+        <v>848.8417899378741</v>
       </c>
       <c r="D57">
-        <v>1649.213841376552</v>
+        <v>1656.681789937874</v>
       </c>
       <c r="E57">
-        <v>25.375</v>
+        <v>40.04000000000008</v>
       </c>
       <c r="F57">
-        <v>806.575</v>
+        <v>821.2400000000001</v>
       </c>
       <c r="G57">
         <v>13.4</v>
@@ -5961,28 +5961,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M57">
-        <v>44.60359750000001</v>
+        <v>45.41457200000001</v>
       </c>
       <c r="N57">
-        <v>168.9630691666667</v>
+        <v>168.1520946666666</v>
       </c>
       <c r="O57">
-        <v>59.13707420833332</v>
+        <v>58.85323313333332</v>
       </c>
       <c r="P57">
-        <v>109.8259949583333</v>
+        <v>109.2988615333333</v>
       </c>
       <c r="Q57">
-        <v>109.9259949583333</v>
+        <v>109.3988615333333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1139439647944519</v>
+        <v>0.1151906176826138</v>
       </c>
       <c r="T57">
-        <v>0.9915777186550718</v>
+        <v>1.009718037178173</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.788104068660978</v>
+        <v>4.702602210292032</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07081307178035008</v>
+        <v>0.0705816094031968</v>
       </c>
       <c r="C58">
-        <v>848.8417899378741</v>
+        <v>841.7126786791708</v>
       </c>
       <c r="D58">
-        <v>1656.681789937874</v>
+        <v>1664.217678679171</v>
       </c>
       <c r="E58">
-        <v>40.04000000000008</v>
+        <v>54.70500000000004</v>
       </c>
       <c r="F58">
-        <v>821.2400000000001</v>
+        <v>835.9050000000001</v>
       </c>
       <c r="G58">
         <v>13.4</v>
@@ -6043,28 +6043,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M58">
-        <v>45.41457200000001</v>
+        <v>46.22554650000001</v>
       </c>
       <c r="N58">
-        <v>168.1520946666666</v>
+        <v>167.3411201666667</v>
       </c>
       <c r="O58">
-        <v>58.85323313333332</v>
+        <v>58.56939205833333</v>
       </c>
       <c r="P58">
-        <v>109.2988615333333</v>
+        <v>108.7717281083333</v>
       </c>
       <c r="Q58">
-        <v>109.3988615333333</v>
+        <v>108.8717281083333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1151906176826138</v>
+        <v>0.1164952544260391</v>
       </c>
       <c r="T58">
-        <v>1.009718037178173</v>
+        <v>1.028702091446535</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.702602210292032</v>
+        <v>4.620100417129014</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0705816094031968</v>
+        <v>0.07035014702604354</v>
       </c>
       <c r="C59">
-        <v>841.7126786791708</v>
+        <v>834.6524389728023</v>
       </c>
       <c r="D59">
-        <v>1664.217678679171</v>
+        <v>1671.822438972802</v>
       </c>
       <c r="E59">
-        <v>54.70500000000004</v>
+        <v>69.37</v>
       </c>
       <c r="F59">
-        <v>835.9050000000001</v>
+        <v>850.5700000000001</v>
       </c>
       <c r="G59">
         <v>13.4</v>
@@ -6125,28 +6125,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M59">
-        <v>46.22554650000001</v>
+        <v>47.03652100000001</v>
       </c>
       <c r="N59">
-        <v>167.3411201666667</v>
+        <v>166.5301456666667</v>
       </c>
       <c r="O59">
-        <v>58.56939205833333</v>
+        <v>58.28555098333333</v>
       </c>
       <c r="P59">
-        <v>108.7717281083333</v>
+        <v>108.2445946833333</v>
       </c>
       <c r="Q59">
-        <v>108.8717281083333</v>
+        <v>108.3445946833333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1164952544260391</v>
+        <v>0.1178620167286751</v>
       </c>
       <c r="T59">
-        <v>1.028702091446535</v>
+        <v>1.048590148299105</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.620100417129014</v>
+        <v>4.54044351338541</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07035014702604356</v>
+        <v>0.07107743464889028</v>
       </c>
       <c r="C60">
-        <v>834.652438972802</v>
+        <v>796.3227950176861</v>
       </c>
       <c r="D60">
-        <v>1671.822438972802</v>
+        <v>1648.157795017686</v>
       </c>
       <c r="E60">
-        <v>69.36999999999989</v>
+        <v>84.03499999999985</v>
       </c>
       <c r="F60">
-        <v>850.5699999999999</v>
+        <v>865.2349999999999</v>
       </c>
       <c r="G60">
         <v>13.4</v>
@@ -6207,45 +6207,45 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M60">
-        <v>47.036521</v>
+        <v>50.010583</v>
       </c>
       <c r="N60">
-        <v>166.5301456666667</v>
+        <v>163.5560836666667</v>
       </c>
       <c r="O60">
-        <v>58.28555098333333</v>
+        <v>57.24462928333333</v>
       </c>
       <c r="P60">
-        <v>108.2445946833333</v>
+        <v>106.3114543833333</v>
       </c>
       <c r="Q60">
-        <v>108.3445946833333</v>
+        <v>106.4114543833333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1178620167286751</v>
+        <v>0.119295450363147</v>
       </c>
       <c r="T60">
-        <v>1.048590148299105</v>
+        <v>1.069448354266434</v>
       </c>
       <c r="U60">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V60">
         <v>0.35</v>
       </c>
       <c r="W60">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>4.54044351338541</v>
+        <v>4.27042945423505</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07107743464889028</v>
+        <v>0.07086222227173702</v>
       </c>
       <c r="C61">
-        <v>796.3227950176861</v>
+        <v>788.590338081067</v>
       </c>
       <c r="D61">
-        <v>1648.157795017686</v>
+        <v>1655.090338081067</v>
       </c>
       <c r="E61">
-        <v>84.03499999999985</v>
+        <v>98.69999999999993</v>
       </c>
       <c r="F61">
-        <v>865.2349999999999</v>
+        <v>879.9</v>
       </c>
       <c r="G61">
         <v>13.4</v>
@@ -6289,28 +6289,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M61">
-        <v>50.010583</v>
+        <v>50.85822</v>
       </c>
       <c r="N61">
-        <v>163.5560836666667</v>
+        <v>162.7084466666666</v>
       </c>
       <c r="O61">
-        <v>57.24462928333333</v>
+        <v>56.94795633333332</v>
       </c>
       <c r="P61">
-        <v>106.3114543833333</v>
+        <v>105.7604903333333</v>
       </c>
       <c r="Q61">
-        <v>106.4114543833333</v>
+        <v>105.8604903333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.119295450363147</v>
+        <v>0.1208005556793425</v>
       </c>
       <c r="T61">
-        <v>1.069448354266434</v>
+        <v>1.09134947053213</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.27042945423505</v>
+        <v>4.199255629997799</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07086222227173702</v>
+        <v>0.07064700989458375</v>
       </c>
       <c r="C62">
-        <v>788.590338081067</v>
+        <v>780.9164473324462</v>
       </c>
       <c r="D62">
-        <v>1655.090338081067</v>
+        <v>1662.081447332446</v>
       </c>
       <c r="E62">
-        <v>98.69999999999993</v>
+        <v>113.3649999999999</v>
       </c>
       <c r="F62">
-        <v>879.9</v>
+        <v>894.5649999999999</v>
       </c>
       <c r="G62">
         <v>13.4</v>
@@ -6371,28 +6371,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M62">
-        <v>50.85822</v>
+        <v>51.705857</v>
       </c>
       <c r="N62">
-        <v>162.7084466666666</v>
+        <v>161.8608096666667</v>
       </c>
       <c r="O62">
-        <v>56.94795633333332</v>
+        <v>56.65128338333332</v>
       </c>
       <c r="P62">
-        <v>105.7604903333333</v>
+        <v>105.2095262833333</v>
       </c>
       <c r="Q62">
-        <v>105.8604903333333</v>
+        <v>105.3095262833333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1208005556793425</v>
+        <v>0.1223828458835481</v>
       </c>
       <c r="T62">
-        <v>1.09134947053213</v>
+        <v>1.114373720965297</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.199255629997799</v>
+        <v>4.130415373768327</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07064700989458375</v>
+        <v>0.07043179751743049</v>
       </c>
       <c r="C63">
-        <v>780.9164473324462</v>
+        <v>773.3018680715184</v>
       </c>
       <c r="D63">
-        <v>1662.081447332446</v>
+        <v>1669.131868071518</v>
       </c>
       <c r="E63">
-        <v>113.3649999999999</v>
+        <v>128.03</v>
       </c>
       <c r="F63">
-        <v>894.5649999999999</v>
+        <v>909.23</v>
       </c>
       <c r="G63">
         <v>13.4</v>
@@ -6453,28 +6453,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M63">
-        <v>51.705857</v>
+        <v>52.55349400000001</v>
       </c>
       <c r="N63">
-        <v>161.8608096666667</v>
+        <v>161.0131726666667</v>
       </c>
       <c r="O63">
-        <v>56.65128338333332</v>
+        <v>56.35461043333333</v>
       </c>
       <c r="P63">
-        <v>105.2095262833333</v>
+        <v>104.6585622333333</v>
       </c>
       <c r="Q63">
-        <v>105.3095262833333</v>
+        <v>104.7585622333333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1223828458835481</v>
+        <v>0.1240484145195539</v>
       </c>
       <c r="T63">
-        <v>1.114373720965297</v>
+        <v>1.138609774052842</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.130415373768327</v>
+        <v>4.063795770965612</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07043179751743049</v>
+        <v>0.07164983514027722</v>
       </c>
       <c r="C64">
-        <v>773.3018680715184</v>
+        <v>719.5038371696101</v>
       </c>
       <c r="D64">
-        <v>1669.131868071518</v>
+        <v>1629.99883716961</v>
       </c>
       <c r="E64">
-        <v>128.03</v>
+        <v>142.6949999999999</v>
       </c>
       <c r="F64">
-        <v>909.23</v>
+        <v>923.895</v>
       </c>
       <c r="G64">
         <v>13.4</v>
@@ -6535,45 +6535,45 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M64">
-        <v>52.55349400000001</v>
+        <v>56.6347635</v>
       </c>
       <c r="N64">
-        <v>161.0131726666667</v>
+        <v>156.9319031666667</v>
       </c>
       <c r="O64">
-        <v>56.35461043333333</v>
+        <v>54.92616610833333</v>
       </c>
       <c r="P64">
-        <v>104.6585622333333</v>
+        <v>102.0057370583333</v>
       </c>
       <c r="Q64">
-        <v>104.7585622333333</v>
+        <v>102.1057370583333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1240484145195539</v>
+        <v>0.1258040138926411</v>
       </c>
       <c r="T64">
-        <v>1.138609774052842</v>
+        <v>1.164155884064037</v>
       </c>
       <c r="U64">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V64">
         <v>0.35</v>
       </c>
       <c r="W64">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.063795770965612</v>
+        <v>3.770946561234721</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07164983514027722</v>
+        <v>0.07145737276312396</v>
       </c>
       <c r="C65">
-        <v>719.5038371696101</v>
+        <v>710.8997374183385</v>
       </c>
       <c r="D65">
-        <v>1629.99883716961</v>
+        <v>1636.059737418338</v>
       </c>
       <c r="E65">
-        <v>142.6949999999999</v>
+        <v>157.36</v>
       </c>
       <c r="F65">
-        <v>923.895</v>
+        <v>938.5600000000001</v>
       </c>
       <c r="G65">
         <v>13.4</v>
@@ -6617,28 +6617,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M65">
-        <v>56.6347635</v>
+        <v>57.533728</v>
       </c>
       <c r="N65">
-        <v>156.9319031666667</v>
+        <v>156.0329386666667</v>
       </c>
       <c r="O65">
-        <v>54.92616610833333</v>
+        <v>54.61152853333333</v>
       </c>
       <c r="P65">
-        <v>102.0057370583333</v>
+        <v>101.4214101333333</v>
       </c>
       <c r="Q65">
-        <v>102.1057370583333</v>
+        <v>101.5214101333333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1258040138926411</v>
+        <v>0.1276571465642332</v>
       </c>
       <c r="T65">
-        <v>1.164155884064037</v>
+        <v>1.191121222409188</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.770946561234721</v>
+        <v>3.712025521215428</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07145737276312396</v>
+        <v>0.07126491038597069</v>
       </c>
       <c r="C66">
-        <v>710.8997374183385</v>
+        <v>702.3408789425986</v>
       </c>
       <c r="D66">
-        <v>1636.059737418338</v>
+        <v>1642.165878942599</v>
       </c>
       <c r="E66">
-        <v>157.36</v>
+        <v>172.025</v>
       </c>
       <c r="F66">
-        <v>938.5600000000001</v>
+        <v>953.225</v>
       </c>
       <c r="G66">
         <v>13.4</v>
@@ -6699,28 +6699,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M66">
-        <v>57.533728</v>
+        <v>58.4326925</v>
       </c>
       <c r="N66">
-        <v>156.0329386666667</v>
+        <v>155.1339741666667</v>
       </c>
       <c r="O66">
-        <v>54.61152853333333</v>
+        <v>54.29689095833333</v>
       </c>
       <c r="P66">
-        <v>101.4214101333333</v>
+        <v>100.8370832083333</v>
       </c>
       <c r="Q66">
-        <v>101.5214101333333</v>
+        <v>100.9370832083333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1276571465642332</v>
+        <v>0.1296161725313448</v>
       </c>
       <c r="T66">
-        <v>1.191121222409188</v>
+        <v>1.219627437231205</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.712025521215428</v>
+        <v>3.654917436273652</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07126491038597069</v>
+        <v>0.07107244800881742</v>
       </c>
       <c r="C67">
-        <v>702.3408789425986</v>
+        <v>693.8277701917689</v>
       </c>
       <c r="D67">
-        <v>1642.165878942599</v>
+        <v>1648.317770191769</v>
       </c>
       <c r="E67">
-        <v>172.025</v>
+        <v>186.6900000000001</v>
       </c>
       <c r="F67">
-        <v>953.225</v>
+        <v>967.8900000000001</v>
       </c>
       <c r="G67">
         <v>13.4</v>
@@ -6781,28 +6781,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M67">
-        <v>58.4326925</v>
+        <v>59.33165700000001</v>
       </c>
       <c r="N67">
-        <v>155.1339741666667</v>
+        <v>154.2350096666667</v>
       </c>
       <c r="O67">
-        <v>54.29689095833333</v>
+        <v>53.98225338333333</v>
       </c>
       <c r="P67">
-        <v>100.8370832083333</v>
+        <v>100.2527562833333</v>
       </c>
       <c r="Q67">
-        <v>100.9370832083333</v>
+        <v>100.3527562833333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1296161725313448</v>
+        <v>0.1316904353200512</v>
       </c>
       <c r="T67">
-        <v>1.219627437231205</v>
+        <v>1.249810488219222</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.654917436273652</v>
+        <v>3.599539899360415</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07107244800881742</v>
+        <v>0.07087998563166417</v>
       </c>
       <c r="C68">
-        <v>693.8277701917689</v>
+        <v>685.360927262901</v>
       </c>
       <c r="D68">
-        <v>1648.317770191769</v>
+        <v>1654.515927262901</v>
       </c>
       <c r="E68">
-        <v>186.6900000000001</v>
+        <v>201.355</v>
       </c>
       <c r="F68">
-        <v>967.8900000000001</v>
+        <v>982.5550000000001</v>
       </c>
       <c r="G68">
         <v>13.4</v>
@@ -6863,28 +6863,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M68">
-        <v>59.33165700000001</v>
+        <v>60.23062150000001</v>
       </c>
       <c r="N68">
-        <v>154.2350096666667</v>
+        <v>153.3360451666667</v>
       </c>
       <c r="O68">
-        <v>53.98225338333333</v>
+        <v>53.66761580833332</v>
       </c>
       <c r="P68">
-        <v>100.2527562833333</v>
+        <v>99.66842935833333</v>
       </c>
       <c r="Q68">
-        <v>100.3527562833333</v>
+        <v>99.76842935833332</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1316904353200512</v>
+        <v>0.1338904110050429</v>
       </c>
       <c r="T68">
-        <v>1.249810488219222</v>
+        <v>1.281822815024696</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.599539899360415</v>
+        <v>3.545815423250557</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07087998563166417</v>
+        <v>0.07192512325451089</v>
       </c>
       <c r="C69">
-        <v>685.360927262901</v>
+        <v>637.5872833662431</v>
       </c>
       <c r="D69">
-        <v>1654.515927262901</v>
+        <v>1621.407283366243</v>
       </c>
       <c r="E69">
-        <v>201.355</v>
+        <v>216.02</v>
       </c>
       <c r="F69">
-        <v>982.5550000000001</v>
+        <v>997.22</v>
       </c>
       <c r="G69">
         <v>13.4</v>
@@ -6945,45 +6945,45 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M69">
-        <v>60.23062150000001</v>
+        <v>63.92180200000001</v>
       </c>
       <c r="N69">
-        <v>153.3360451666667</v>
+        <v>149.6448646666666</v>
       </c>
       <c r="O69">
-        <v>53.66761580833332</v>
+        <v>52.37570263333333</v>
       </c>
       <c r="P69">
-        <v>99.66842935833333</v>
+        <v>97.26916203333332</v>
       </c>
       <c r="Q69">
-        <v>99.76842935833332</v>
+        <v>97.36916203333331</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1338904110050429</v>
+        <v>0.1362278851703466</v>
       </c>
       <c r="T69">
-        <v>1.281822815024696</v>
+        <v>1.315835912255511</v>
       </c>
       <c r="U69">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V69">
         <v>0.35</v>
       </c>
       <c r="W69">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.545815423250557</v>
+        <v>3.341061421683116</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07192512325451089</v>
+        <v>0.07175086087735763</v>
       </c>
       <c r="C70">
-        <v>637.5872833662431</v>
+        <v>628.3503377508604</v>
       </c>
       <c r="D70">
-        <v>1621.407283366243</v>
+        <v>1626.83533775086</v>
       </c>
       <c r="E70">
-        <v>216.02</v>
+        <v>230.6850000000001</v>
       </c>
       <c r="F70">
-        <v>997.22</v>
+        <v>1011.885</v>
       </c>
       <c r="G70">
         <v>13.4</v>
@@ -7027,28 +7027,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M70">
-        <v>63.92180200000001</v>
+        <v>64.86182850000002</v>
       </c>
       <c r="N70">
-        <v>149.6448646666666</v>
+        <v>148.7048381666667</v>
       </c>
       <c r="O70">
-        <v>52.37570263333333</v>
+        <v>52.04669335833333</v>
       </c>
       <c r="P70">
-        <v>97.26916203333332</v>
+        <v>96.65814480833333</v>
       </c>
       <c r="Q70">
-        <v>97.36916203333331</v>
+        <v>96.75814480833333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1362278851703466</v>
+        <v>0.1387161641205085</v>
       </c>
       <c r="T70">
-        <v>1.315835912255511</v>
+        <v>1.352043402856057</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.341061421683116</v>
+        <v>3.292640241658723</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07175086087735763</v>
+        <v>0.07157659850020437</v>
       </c>
       <c r="C71">
-        <v>628.3503377508604</v>
+        <v>619.1498576715117</v>
       </c>
       <c r="D71">
-        <v>1626.83533775086</v>
+        <v>1632.299857671512</v>
       </c>
       <c r="E71">
-        <v>230.6850000000001</v>
+        <v>245.3500000000001</v>
       </c>
       <c r="F71">
-        <v>1011.885</v>
+        <v>1026.55</v>
       </c>
       <c r="G71">
         <v>13.4</v>
@@ -7109,28 +7109,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M71">
-        <v>64.86182850000002</v>
+        <v>65.80185500000002</v>
       </c>
       <c r="N71">
-        <v>148.7048381666667</v>
+        <v>147.7648116666666</v>
       </c>
       <c r="O71">
-        <v>52.04669335833333</v>
+        <v>51.71768408333332</v>
       </c>
       <c r="P71">
-        <v>96.65814480833333</v>
+        <v>96.04712758333332</v>
       </c>
       <c r="Q71">
-        <v>96.75814480833333</v>
+        <v>96.14712758333332</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1387161641205085</v>
+        <v>0.1413703283340146</v>
       </c>
       <c r="T71">
-        <v>1.352043402856057</v>
+        <v>1.390664726163305</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.292640241658723</v>
+        <v>3.24560252392074</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07157659850020437</v>
+        <v>0.07140233612305111</v>
       </c>
       <c r="C72">
-        <v>619.1498576715117</v>
+        <v>609.9862118285205</v>
       </c>
       <c r="D72">
-        <v>1632.299857671512</v>
+        <v>1637.801211828521</v>
       </c>
       <c r="E72">
-        <v>245.3500000000001</v>
+        <v>260.0150000000001</v>
       </c>
       <c r="F72">
-        <v>1026.55</v>
+        <v>1041.215</v>
       </c>
       <c r="G72">
         <v>13.4</v>
@@ -7191,28 +7191,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M72">
-        <v>65.80185500000002</v>
+        <v>66.74188150000002</v>
       </c>
       <c r="N72">
-        <v>147.7648116666666</v>
+        <v>146.8247851666666</v>
       </c>
       <c r="O72">
-        <v>51.71768408333332</v>
+        <v>51.38867480833332</v>
       </c>
       <c r="P72">
-        <v>96.04712758333332</v>
+        <v>95.43611035833331</v>
       </c>
       <c r="Q72">
-        <v>96.14712758333332</v>
+        <v>95.5361103583333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1413703283340146</v>
+        <v>0.1442075383553486</v>
       </c>
       <c r="T72">
-        <v>1.390664726163305</v>
+        <v>1.431949589008985</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.24560252392074</v>
+        <v>3.199889812316223</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07140233612305111</v>
+        <v>0.07122807374589785</v>
       </c>
       <c r="C73">
-        <v>609.9862118285207</v>
+        <v>600.8597739095533</v>
       </c>
       <c r="D73">
-        <v>1637.801211828521</v>
+        <v>1643.339773909553</v>
       </c>
       <c r="E73">
-        <v>260.0149999999999</v>
+        <v>274.6799999999998</v>
       </c>
       <c r="F73">
-        <v>1041.215</v>
+        <v>1055.88</v>
       </c>
       <c r="G73">
         <v>13.4</v>
@@ -7273,28 +7273,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M73">
-        <v>66.74188150000001</v>
+        <v>67.68190799999999</v>
       </c>
       <c r="N73">
-        <v>146.8247851666667</v>
+        <v>145.8847586666667</v>
       </c>
       <c r="O73">
-        <v>51.38867480833333</v>
+        <v>51.05966553333333</v>
       </c>
       <c r="P73">
-        <v>95.43611035833334</v>
+        <v>94.82509313333334</v>
       </c>
       <c r="Q73">
-        <v>95.53611035833333</v>
+        <v>94.92509313333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1442075383553486</v>
+        <v>0.1472474062353494</v>
       </c>
       <c r="T73">
-        <v>1.431949589008984</v>
+        <v>1.476183370629355</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.199889812316224</v>
+        <v>3.155446898256277</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07122807374589785</v>
+        <v>0.07105381136874457</v>
       </c>
       <c r="C74">
-        <v>600.8597739095533</v>
+        <v>591.770922674237</v>
       </c>
       <c r="D74">
-        <v>1643.339773909553</v>
+        <v>1648.915922674237</v>
       </c>
       <c r="E74">
-        <v>274.6799999999998</v>
+        <v>289.345</v>
       </c>
       <c r="F74">
-        <v>1055.88</v>
+        <v>1070.545</v>
       </c>
       <c r="G74">
         <v>13.4</v>
@@ -7355,28 +7355,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M74">
-        <v>67.68190799999999</v>
+        <v>68.62193450000001</v>
       </c>
       <c r="N74">
-        <v>145.8847586666667</v>
+        <v>144.9447321666667</v>
       </c>
       <c r="O74">
-        <v>51.05966553333333</v>
+        <v>50.73065625833333</v>
       </c>
       <c r="P74">
-        <v>94.82509313333334</v>
+        <v>94.21407590833333</v>
       </c>
       <c r="Q74">
-        <v>94.92509313333333</v>
+        <v>94.31407590833332</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1472474062353494</v>
+        <v>0.1505124495138687</v>
       </c>
       <c r="T74">
-        <v>1.476183370629355</v>
+        <v>1.523693728666049</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.155446898256277</v>
+        <v>3.112221598280163</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07105381136874457</v>
+        <v>0.0708795489915913</v>
       </c>
       <c r="C75">
-        <v>591.770922674237</v>
+        <v>582.7200420405004</v>
       </c>
       <c r="D75">
-        <v>1648.915922674237</v>
+        <v>1654.5300420405</v>
       </c>
       <c r="E75">
-        <v>289.345</v>
+        <v>304.01</v>
       </c>
       <c r="F75">
-        <v>1070.545</v>
+        <v>1085.21</v>
       </c>
       <c r="G75">
         <v>13.4</v>
@@ -7437,28 +7437,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M75">
-        <v>68.62193450000001</v>
+        <v>69.56196100000001</v>
       </c>
       <c r="N75">
-        <v>144.9447321666667</v>
+        <v>144.0047056666667</v>
       </c>
       <c r="O75">
-        <v>50.73065625833333</v>
+        <v>50.40164698333333</v>
       </c>
       <c r="P75">
-        <v>94.21407590833333</v>
+        <v>93.60305868333333</v>
       </c>
       <c r="Q75">
-        <v>94.31407590833332</v>
+        <v>93.70305868333332</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1505124495138687</v>
+        <v>0.1540286499676588</v>
       </c>
       <c r="T75">
-        <v>1.523693728666049</v>
+        <v>1.574858729628643</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.112221598280163</v>
+        <v>3.070164549654755</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0708795489915913</v>
+        <v>0.07070528661443803</v>
       </c>
       <c r="C76">
-        <v>582.7200420405004</v>
+        <v>573.7075211726874</v>
       </c>
       <c r="D76">
-        <v>1654.5300420405</v>
+        <v>1660.182521172687</v>
       </c>
       <c r="E76">
-        <v>304.01</v>
+        <v>318.675</v>
       </c>
       <c r="F76">
-        <v>1085.21</v>
+        <v>1099.875</v>
       </c>
       <c r="G76">
         <v>13.4</v>
@@ -7519,28 +7519,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M76">
-        <v>69.56196100000001</v>
+        <v>70.5019875</v>
       </c>
       <c r="N76">
-        <v>144.0047056666667</v>
+        <v>143.0646791666667</v>
       </c>
       <c r="O76">
-        <v>50.40164698333333</v>
+        <v>50.07263770833333</v>
       </c>
       <c r="P76">
-        <v>93.60305868333333</v>
+        <v>92.99204145833335</v>
       </c>
       <c r="Q76">
-        <v>93.70305868333332</v>
+        <v>93.09204145833334</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1540286499676588</v>
+        <v>0.1578261464577521</v>
       </c>
       <c r="T76">
-        <v>1.574858729628643</v>
+        <v>1.630116930668245</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.070164549654755</v>
+        <v>3.029229022326026</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07070528661443803</v>
+        <v>0.07438422423728477</v>
       </c>
       <c r="C77">
-        <v>573.7075211726874</v>
+        <v>447.3578170038529</v>
       </c>
       <c r="D77">
-        <v>1660.182521172687</v>
+        <v>1548.497817003853</v>
       </c>
       <c r="E77">
-        <v>318.675</v>
+        <v>333.3399999999999</v>
       </c>
       <c r="F77">
-        <v>1099.875</v>
+        <v>1114.54</v>
       </c>
       <c r="G77">
         <v>13.4</v>
@@ -7601,45 +7601,45 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M77">
-        <v>70.5019875</v>
+        <v>80.13542600000001</v>
       </c>
       <c r="N77">
-        <v>143.0646791666667</v>
+        <v>133.4312406666667</v>
       </c>
       <c r="O77">
-        <v>50.07263770833333</v>
+        <v>46.70093423333333</v>
       </c>
       <c r="P77">
-        <v>92.99204145833335</v>
+        <v>86.73030643333334</v>
       </c>
       <c r="Q77">
-        <v>93.09204145833334</v>
+        <v>86.83030643333333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1578261464577521</v>
+        <v>0.1619401009886866</v>
       </c>
       <c r="T77">
-        <v>1.630116930668245</v>
+        <v>1.68997998179448</v>
       </c>
       <c r="U77">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V77">
         <v>0.35</v>
       </c>
       <c r="W77">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.029229022326026</v>
+        <v>2.665071833107453</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07438422423728477</v>
+        <v>0.0742606618601315</v>
       </c>
       <c r="C78">
-        <v>447.3578170038529</v>
+        <v>436.1994851111788</v>
       </c>
       <c r="D78">
-        <v>1548.497817003853</v>
+        <v>1552.004485111179</v>
       </c>
       <c r="E78">
-        <v>333.3399999999999</v>
+        <v>348.0049999999999</v>
       </c>
       <c r="F78">
-        <v>1114.54</v>
+        <v>1129.205</v>
       </c>
       <c r="G78">
         <v>13.4</v>
@@ -7683,28 +7683,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M78">
-        <v>80.13542600000001</v>
+        <v>81.18983950000001</v>
       </c>
       <c r="N78">
-        <v>133.4312406666667</v>
+        <v>132.3768271666667</v>
       </c>
       <c r="O78">
-        <v>46.70093423333333</v>
+        <v>46.33188950833333</v>
       </c>
       <c r="P78">
-        <v>86.73030643333334</v>
+        <v>86.04493765833334</v>
       </c>
       <c r="Q78">
-        <v>86.83030643333333</v>
+        <v>86.14493765833333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1619401009886866</v>
+        <v>0.1664117906962239</v>
       </c>
       <c r="T78">
-        <v>1.68997998179448</v>
+        <v>1.755048515627344</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.665071833107453</v>
+        <v>2.630460510599564</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0742606618601315</v>
+        <v>0.07413709948297825</v>
       </c>
       <c r="C79">
-        <v>436.1994851111788</v>
+        <v>425.0570713954119</v>
       </c>
       <c r="D79">
-        <v>1552.004485111179</v>
+        <v>1555.527071395412</v>
       </c>
       <c r="E79">
-        <v>348.0049999999999</v>
+        <v>362.6700000000001</v>
       </c>
       <c r="F79">
-        <v>1129.205</v>
+        <v>1143.87</v>
       </c>
       <c r="G79">
         <v>13.4</v>
@@ -7765,28 +7765,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M79">
-        <v>81.18983950000001</v>
+        <v>82.24425300000001</v>
       </c>
       <c r="N79">
-        <v>132.3768271666667</v>
+        <v>131.3224136666666</v>
       </c>
       <c r="O79">
-        <v>46.33188950833333</v>
+        <v>45.96284478333332</v>
       </c>
       <c r="P79">
-        <v>86.04493765833334</v>
+        <v>85.35956888333332</v>
       </c>
       <c r="Q79">
-        <v>86.14493765833333</v>
+        <v>85.45956888333332</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1664117906962239</v>
+        <v>0.1712899976499011</v>
       </c>
       <c r="T79">
-        <v>1.755048515627344</v>
+        <v>1.826032370717741</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.630460510599564</v>
+        <v>2.596736657899569</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07413709948297825</v>
+        <v>0.07401353710582498</v>
       </c>
       <c r="C80">
-        <v>425.0570713954119</v>
+        <v>413.9306844916341</v>
       </c>
       <c r="D80">
-        <v>1555.527071395412</v>
+        <v>1559.065684491634</v>
       </c>
       <c r="E80">
-        <v>362.6700000000001</v>
+        <v>377.335</v>
       </c>
       <c r="F80">
-        <v>1143.87</v>
+        <v>1158.535</v>
       </c>
       <c r="G80">
         <v>13.4</v>
@@ -7847,28 +7847,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M80">
-        <v>82.24425300000001</v>
+        <v>83.29866650000001</v>
       </c>
       <c r="N80">
-        <v>131.3224136666666</v>
+        <v>130.2680001666666</v>
       </c>
       <c r="O80">
-        <v>45.96284478333332</v>
+        <v>45.59380005833332</v>
       </c>
       <c r="P80">
-        <v>85.35956888333332</v>
+        <v>84.67420010833331</v>
       </c>
       <c r="Q80">
-        <v>85.45956888333332</v>
+        <v>84.7742001083333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1712899976499011</v>
+        <v>0.1766327957420237</v>
       </c>
       <c r="T80">
-        <v>1.826032370717741</v>
+        <v>1.903776592959605</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.596736657899569</v>
+        <v>2.563866573622359</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07401353710582498</v>
+        <v>0.0738899747286717</v>
       </c>
       <c r="C81">
-        <v>413.9306844916341</v>
+        <v>402.8204340256987</v>
       </c>
       <c r="D81">
-        <v>1559.065684491634</v>
+        <v>1562.620434025699</v>
       </c>
       <c r="E81">
-        <v>377.335</v>
+        <v>392</v>
       </c>
       <c r="F81">
-        <v>1158.535</v>
+        <v>1173.2</v>
       </c>
       <c r="G81">
         <v>13.4</v>
@@ -7929,28 +7929,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M81">
-        <v>83.29866650000001</v>
+        <v>84.35308000000001</v>
       </c>
       <c r="N81">
-        <v>130.2680001666666</v>
+        <v>129.2135866666667</v>
       </c>
       <c r="O81">
-        <v>45.59380005833332</v>
+        <v>45.22475533333333</v>
       </c>
       <c r="P81">
-        <v>84.67420010833331</v>
+        <v>83.98883133333334</v>
       </c>
       <c r="Q81">
-        <v>84.7742001083333</v>
+        <v>84.08883133333333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1766327957420237</v>
+        <v>0.1825098736433586</v>
       </c>
       <c r="T81">
-        <v>1.903776592959605</v>
+        <v>1.989295237425655</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.563866573622359</v>
+        <v>2.53181824145208</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0738899747286717</v>
+        <v>0.07376641235151846</v>
       </c>
       <c r="C82">
-        <v>402.8204340256987</v>
+        <v>391.7264306255543</v>
       </c>
       <c r="D82">
-        <v>1562.620434025699</v>
+        <v>1566.191430625554</v>
       </c>
       <c r="E82">
-        <v>392</v>
+        <v>406.665</v>
       </c>
       <c r="F82">
-        <v>1173.2</v>
+        <v>1187.865</v>
       </c>
       <c r="G82">
         <v>13.4</v>
@@ -8011,28 +8011,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M82">
-        <v>84.35308000000001</v>
+        <v>85.4074935</v>
       </c>
       <c r="N82">
-        <v>129.2135866666667</v>
+        <v>128.1591731666667</v>
       </c>
       <c r="O82">
-        <v>45.22475533333333</v>
+        <v>44.85571060833333</v>
       </c>
       <c r="P82">
-        <v>83.98883133333334</v>
+        <v>83.30346255833334</v>
       </c>
       <c r="Q82">
-        <v>84.08883133333333</v>
+        <v>83.40346255833333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1825098736433586</v>
+        <v>0.1890055913237813</v>
       </c>
       <c r="T82">
-        <v>1.989295237425655</v>
+        <v>2.083815844467079</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.53181824145208</v>
+        <v>2.500561226125511</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07376641235151846</v>
+        <v>0.0757215499743652</v>
       </c>
       <c r="C83">
-        <v>391.7264306255543</v>
+        <v>322.4045193821182</v>
       </c>
       <c r="D83">
-        <v>1566.191430625554</v>
+        <v>1511.534519382118</v>
       </c>
       <c r="E83">
-        <v>406.665</v>
+        <v>421.3300000000002</v>
       </c>
       <c r="F83">
-        <v>1187.865</v>
+        <v>1202.53</v>
       </c>
       <c r="G83">
         <v>13.4</v>
@@ -8093,45 +8093,45 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M83">
-        <v>85.4074935</v>
+        <v>91.15177400000002</v>
       </c>
       <c r="N83">
-        <v>128.1591731666667</v>
+        <v>122.4148926666666</v>
       </c>
       <c r="O83">
-        <v>44.85571060833333</v>
+        <v>42.84521243333332</v>
       </c>
       <c r="P83">
-        <v>83.30346255833334</v>
+        <v>79.56968023333332</v>
       </c>
       <c r="Q83">
-        <v>83.40346255833333</v>
+        <v>79.66968023333331</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1890055913237813</v>
+        <v>0.1962230554131399</v>
       </c>
       <c r="T83">
-        <v>2.083815844467079</v>
+        <v>2.188838741179772</v>
       </c>
       <c r="U83">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V83">
         <v>0.35</v>
       </c>
       <c r="W83">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y83">
-        <v>2.500561226125511</v>
+        <v>2.342978718841683</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0757215499743652</v>
+        <v>0.07562333759721193</v>
       </c>
       <c r="C84">
-        <v>322.4045193821182</v>
+        <v>310.3939366908282</v>
       </c>
       <c r="D84">
-        <v>1511.534519382118</v>
+        <v>1514.188936690828</v>
       </c>
       <c r="E84">
-        <v>421.3300000000002</v>
+        <v>435.9950000000001</v>
       </c>
       <c r="F84">
-        <v>1202.53</v>
+        <v>1217.195</v>
       </c>
       <c r="G84">
         <v>13.4</v>
@@ -8175,28 +8175,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M84">
-        <v>91.15177400000002</v>
+        <v>92.26338100000002</v>
       </c>
       <c r="N84">
-        <v>122.4148926666666</v>
+        <v>121.3032856666666</v>
       </c>
       <c r="O84">
-        <v>42.84521243333332</v>
+        <v>42.45614998333332</v>
       </c>
       <c r="P84">
-        <v>79.56968023333332</v>
+        <v>78.84713568333332</v>
       </c>
       <c r="Q84">
-        <v>79.66968023333331</v>
+        <v>78.94713568333331</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1962230554131399</v>
+        <v>0.2042896329247761</v>
       </c>
       <c r="T84">
-        <v>2.188838741179772</v>
+        <v>2.306217272799841</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.342978718841683</v>
+        <v>2.31475005957853</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07562333759721193</v>
+        <v>0.07552512522005866</v>
       </c>
       <c r="C85">
-        <v>310.3939366908282</v>
+        <v>298.3926932853287</v>
       </c>
       <c r="D85">
-        <v>1514.188936690828</v>
+        <v>1516.852693285329</v>
       </c>
       <c r="E85">
-        <v>435.9950000000001</v>
+        <v>450.6600000000001</v>
       </c>
       <c r="F85">
-        <v>1217.195</v>
+        <v>1231.86</v>
       </c>
       <c r="G85">
         <v>13.4</v>
@@ -8257,28 +8257,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M85">
-        <v>92.26338100000002</v>
+        <v>93.37498800000002</v>
       </c>
       <c r="N85">
-        <v>121.3032856666666</v>
+        <v>120.1916786666666</v>
       </c>
       <c r="O85">
-        <v>42.45614998333332</v>
+        <v>42.06708753333332</v>
       </c>
       <c r="P85">
-        <v>78.84713568333332</v>
+        <v>78.12459113333333</v>
       </c>
       <c r="Q85">
-        <v>78.94713568333331</v>
+        <v>78.22459113333332</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2042896329247761</v>
+        <v>0.2133645326253666</v>
       </c>
       <c r="T85">
-        <v>2.306217272799841</v>
+        <v>2.438268120872418</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.31475005957853</v>
+        <v>2.287193511250214</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07552512522005866</v>
+        <v>0.0754269128429054</v>
       </c>
       <c r="C86">
-        <v>298.392693285329</v>
+        <v>286.4008385414124</v>
       </c>
       <c r="D86">
-        <v>1516.852693285329</v>
+        <v>1519.525838541412</v>
       </c>
       <c r="E86">
-        <v>450.6599999999999</v>
+        <v>465.3249999999998</v>
       </c>
       <c r="F86">
-        <v>1231.86</v>
+        <v>1246.525</v>
       </c>
       <c r="G86">
         <v>13.4</v>
@@ -8339,28 +8339,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M86">
-        <v>93.374988</v>
+        <v>94.48659499999999</v>
       </c>
       <c r="N86">
-        <v>120.1916786666667</v>
+        <v>119.0800716666667</v>
       </c>
       <c r="O86">
-        <v>42.06708753333333</v>
+        <v>41.67802508333333</v>
       </c>
       <c r="P86">
-        <v>78.12459113333333</v>
+        <v>77.40204658333334</v>
       </c>
       <c r="Q86">
-        <v>78.22459113333332</v>
+        <v>77.50204658333334</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2133645326253666</v>
+        <v>0.2236494189527026</v>
       </c>
       <c r="T86">
-        <v>2.438268120872417</v>
+        <v>2.587925748688005</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.287193511250215</v>
+        <v>2.26028535229433</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0754269128429054</v>
+        <v>0.07532870046575213</v>
       </c>
       <c r="C87">
-        <v>286.4008385414124</v>
+        <v>274.4184221835433</v>
       </c>
       <c r="D87">
-        <v>1519.525838541412</v>
+        <v>1522.208422183543</v>
       </c>
       <c r="E87">
-        <v>465.3249999999998</v>
+        <v>479.99</v>
       </c>
       <c r="F87">
-        <v>1246.525</v>
+        <v>1261.19</v>
       </c>
       <c r="G87">
         <v>13.4</v>
@@ -8421,28 +8421,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M87">
-        <v>94.48659499999999</v>
+        <v>95.59820200000001</v>
       </c>
       <c r="N87">
-        <v>119.0800716666667</v>
+        <v>117.9684646666666</v>
       </c>
       <c r="O87">
-        <v>41.67802508333333</v>
+        <v>41.28896263333333</v>
       </c>
       <c r="P87">
-        <v>77.40204658333334</v>
+        <v>76.67950203333332</v>
       </c>
       <c r="Q87">
-        <v>77.50204658333334</v>
+        <v>76.77950203333332</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2236494189527026</v>
+        <v>0.2354035747553723</v>
       </c>
       <c r="T87">
-        <v>2.587925748688005</v>
+        <v>2.758963037620104</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.26028535229433</v>
+        <v>2.234002964476954</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07532870046575213</v>
+        <v>0.07523048808859886</v>
       </c>
       <c r="C88">
-        <v>274.4184221835433</v>
+        <v>262.4454942879449</v>
       </c>
       <c r="D88">
-        <v>1522.208422183543</v>
+        <v>1524.900494287945</v>
       </c>
       <c r="E88">
-        <v>479.99</v>
+        <v>494.655</v>
       </c>
       <c r="F88">
-        <v>1261.19</v>
+        <v>1275.855</v>
       </c>
       <c r="G88">
         <v>13.4</v>
@@ -8503,28 +8503,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M88">
-        <v>95.59820200000001</v>
+        <v>96.70980900000001</v>
       </c>
       <c r="N88">
-        <v>117.9684646666666</v>
+        <v>116.8568576666667</v>
       </c>
       <c r="O88">
-        <v>41.28896263333333</v>
+        <v>40.89990018333333</v>
       </c>
       <c r="P88">
-        <v>76.67950203333332</v>
+        <v>75.95695748333333</v>
       </c>
       <c r="Q88">
-        <v>76.77950203333332</v>
+        <v>76.05695748333332</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2354035747553723</v>
+        <v>0.2489660622199912</v>
       </c>
       <c r="T88">
-        <v>2.758963037620104</v>
+        <v>2.956313755618681</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.234002964476954</v>
+        <v>2.208324769482966</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07523048808859886</v>
+        <v>0.0751322757114456</v>
       </c>
       <c r="C89">
-        <v>262.4454942879449</v>
+        <v>250.4821052857119</v>
       </c>
       <c r="D89">
-        <v>1524.900494287945</v>
+        <v>1527.602105285712</v>
       </c>
       <c r="E89">
-        <v>494.655</v>
+        <v>509.3199999999999</v>
       </c>
       <c r="F89">
-        <v>1275.855</v>
+        <v>1290.52</v>
       </c>
       <c r="G89">
         <v>13.4</v>
@@ -8585,28 +8585,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M89">
-        <v>96.70980900000001</v>
+        <v>97.82141600000001</v>
       </c>
       <c r="N89">
-        <v>116.8568576666667</v>
+        <v>115.7452506666666</v>
       </c>
       <c r="O89">
-        <v>40.89990018333333</v>
+        <v>40.51083773333333</v>
       </c>
       <c r="P89">
-        <v>75.95695748333333</v>
+        <v>75.23441293333332</v>
       </c>
       <c r="Q89">
-        <v>76.05695748333332</v>
+        <v>75.33441293333331</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2489660622199912</v>
+        <v>0.2647889642620466</v>
       </c>
       <c r="T89">
-        <v>2.956313755618681</v>
+        <v>3.186556259950355</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.208324769482966</v>
+        <v>2.18323016982975</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0751322757114456</v>
+        <v>0.07503406333429233</v>
       </c>
       <c r="C90">
-        <v>250.4821052857119</v>
+        <v>238.5283059659619</v>
       </c>
       <c r="D90">
-        <v>1527.602105285712</v>
+        <v>1530.313305965962</v>
       </c>
       <c r="E90">
-        <v>509.3199999999999</v>
+        <v>523.9849999999999</v>
       </c>
       <c r="F90">
-        <v>1290.52</v>
+        <v>1305.185</v>
       </c>
       <c r="G90">
         <v>13.4</v>
@@ -8667,28 +8667,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M90">
-        <v>97.82141600000001</v>
+        <v>98.93302300000001</v>
       </c>
       <c r="N90">
-        <v>115.7452506666666</v>
+        <v>114.6336436666667</v>
       </c>
       <c r="O90">
-        <v>40.51083773333333</v>
+        <v>40.12177528333333</v>
       </c>
       <c r="P90">
-        <v>75.23441293333332</v>
+        <v>74.51186838333334</v>
       </c>
       <c r="Q90">
-        <v>75.33441293333331</v>
+        <v>74.61186838333333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2647889642620466</v>
+        <v>0.2834887575844757</v>
       </c>
       <c r="T90">
-        <v>3.186556259950355</v>
+        <v>3.458661037796877</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.18323016982975</v>
+        <v>2.158699493764248</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07503406333429233</v>
+        <v>0.07493585095713906</v>
       </c>
       <c r="C91">
-        <v>238.5283059659619</v>
+        <v>226.5841474790163</v>
       </c>
       <c r="D91">
-        <v>1530.313305965962</v>
+        <v>1533.034147479016</v>
       </c>
       <c r="E91">
-        <v>523.9849999999999</v>
+        <v>538.6500000000001</v>
       </c>
       <c r="F91">
-        <v>1305.185</v>
+        <v>1319.85</v>
       </c>
       <c r="G91">
         <v>13.4</v>
@@ -8749,28 +8749,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M91">
-        <v>98.93302300000001</v>
+        <v>100.04463</v>
       </c>
       <c r="N91">
-        <v>114.6336436666667</v>
+        <v>113.5220366666667</v>
       </c>
       <c r="O91">
-        <v>40.12177528333333</v>
+        <v>39.73271283333332</v>
       </c>
       <c r="P91">
-        <v>74.51186838333334</v>
+        <v>73.78932383333333</v>
       </c>
       <c r="Q91">
-        <v>74.61186838333333</v>
+        <v>73.88932383333332</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2834887575844757</v>
+        <v>0.3059285095713906</v>
       </c>
       <c r="T91">
-        <v>3.458661037796877</v>
+        <v>3.785186771212705</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.158699493764248</v>
+        <v>2.134713943833534</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07493585095713906</v>
+        <v>0.07483763857998579</v>
       </c>
       <c r="C92">
-        <v>226.5841474790163</v>
+        <v>214.6496813396202</v>
       </c>
       <c r="D92">
-        <v>1533.034147479016</v>
+        <v>1535.76468133962</v>
       </c>
       <c r="E92">
-        <v>538.6500000000001</v>
+        <v>553.3150000000001</v>
       </c>
       <c r="F92">
-        <v>1319.85</v>
+        <v>1334.515</v>
       </c>
       <c r="G92">
         <v>13.4</v>
@@ -8831,28 +8831,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M92">
-        <v>100.04463</v>
+        <v>101.156237</v>
       </c>
       <c r="N92">
-        <v>113.5220366666667</v>
+        <v>112.4104296666666</v>
       </c>
       <c r="O92">
-        <v>39.73271283333332</v>
+        <v>39.34365038333333</v>
       </c>
       <c r="P92">
-        <v>73.78932383333333</v>
+        <v>73.06677928333332</v>
       </c>
       <c r="Q92">
-        <v>73.88932383333332</v>
+        <v>73.16677928333331</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3059285095713906</v>
+        <v>0.3333548731109534</v>
       </c>
       <c r="T92">
-        <v>3.785186771212705</v>
+        <v>4.184273778720939</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.134713943833534</v>
+        <v>2.111255548846351</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07483763857998579</v>
+        <v>0.07473942620283254</v>
       </c>
       <c r="C93">
-        <v>214.6496813396202</v>
+        <v>202.7249594301888</v>
       </c>
       <c r="D93">
-        <v>1535.76468133962</v>
+        <v>1538.504959430189</v>
       </c>
       <c r="E93">
-        <v>553.3150000000001</v>
+        <v>567.98</v>
       </c>
       <c r="F93">
-        <v>1334.515</v>
+        <v>1349.18</v>
       </c>
       <c r="G93">
         <v>13.4</v>
@@ -8913,28 +8913,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M93">
-        <v>101.156237</v>
+        <v>102.267844</v>
       </c>
       <c r="N93">
-        <v>112.4104296666666</v>
+        <v>111.2988226666667</v>
       </c>
       <c r="O93">
-        <v>39.34365038333333</v>
+        <v>38.95458793333333</v>
       </c>
       <c r="P93">
-        <v>73.06677928333332</v>
+        <v>72.34423473333332</v>
       </c>
       <c r="Q93">
-        <v>73.16677928333331</v>
+        <v>72.44423473333332</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3333548731109534</v>
+        <v>0.3676378275354067</v>
       </c>
       <c r="T93">
-        <v>4.184273778720939</v>
+        <v>4.683132538106231</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.111255548846351</v>
+        <v>2.088307118967587</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07473942620283254</v>
+        <v>0.07464121382567926</v>
       </c>
       <c r="C94">
-        <v>202.7249594301888</v>
+        <v>190.8100340040987</v>
       </c>
       <c r="D94">
-        <v>1538.504959430189</v>
+        <v>1541.255034004099</v>
       </c>
       <c r="E94">
-        <v>567.98</v>
+        <v>582.645</v>
       </c>
       <c r="F94">
-        <v>1349.18</v>
+        <v>1363.845</v>
       </c>
       <c r="G94">
         <v>13.4</v>
@@ -8995,28 +8995,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M94">
-        <v>102.267844</v>
+        <v>103.379451</v>
       </c>
       <c r="N94">
-        <v>111.2988226666667</v>
+        <v>110.1872156666666</v>
       </c>
       <c r="O94">
-        <v>38.95458793333333</v>
+        <v>38.56552548333332</v>
       </c>
       <c r="P94">
-        <v>72.34423473333332</v>
+        <v>71.62169018333333</v>
       </c>
       <c r="Q94">
-        <v>72.44423473333332</v>
+        <v>71.72169018333332</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3676378275354067</v>
+        <v>0.4117159117954182</v>
       </c>
       <c r="T94">
-        <v>4.683132538106231</v>
+        <v>5.324522371601606</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.088307118967587</v>
+        <v>2.065852203709871</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07464121382567926</v>
+        <v>0.07454300144852601</v>
       </c>
       <c r="C95">
-        <v>190.8100340040987</v>
+        <v>178.9049576890045</v>
       </c>
       <c r="D95">
-        <v>1541.255034004099</v>
+        <v>1544.014957689004</v>
       </c>
       <c r="E95">
-        <v>582.645</v>
+        <v>597.3099999999999</v>
       </c>
       <c r="F95">
-        <v>1363.845</v>
+        <v>1378.51</v>
       </c>
       <c r="G95">
         <v>13.4</v>
@@ -9077,28 +9077,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M95">
-        <v>103.379451</v>
+        <v>104.491058</v>
       </c>
       <c r="N95">
-        <v>110.1872156666666</v>
+        <v>109.0756086666667</v>
       </c>
       <c r="O95">
-        <v>38.56552548333332</v>
+        <v>38.17646303333333</v>
       </c>
       <c r="P95">
-        <v>71.62169018333333</v>
+        <v>70.89914563333332</v>
       </c>
       <c r="Q95">
-        <v>71.72169018333332</v>
+        <v>70.99914563333331</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4117159117954182</v>
+        <v>0.470486690808767</v>
       </c>
       <c r="T95">
-        <v>5.324522371601606</v>
+        <v>6.179708816262109</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.065852203709871</v>
+        <v>2.043875052606575</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07454300144852601</v>
+        <v>0.07444478907137274</v>
       </c>
       <c r="C96">
-        <v>178.9049576890045</v>
+        <v>167.0097834901997</v>
       </c>
       <c r="D96">
-        <v>1544.014957689004</v>
+        <v>1546.7847834902</v>
       </c>
       <c r="E96">
-        <v>597.3099999999999</v>
+        <v>611.9750000000001</v>
       </c>
       <c r="F96">
-        <v>1378.51</v>
+        <v>1393.175</v>
       </c>
       <c r="G96">
         <v>13.4</v>
@@ -9159,28 +9159,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M96">
-        <v>104.491058</v>
+        <v>105.602665</v>
       </c>
       <c r="N96">
-        <v>109.0756086666667</v>
+        <v>107.9640016666666</v>
       </c>
       <c r="O96">
-        <v>38.17646303333333</v>
+        <v>37.78740058333332</v>
       </c>
       <c r="P96">
-        <v>70.89914563333332</v>
+        <v>70.17660108333332</v>
       </c>
       <c r="Q96">
-        <v>70.99914563333331</v>
+        <v>70.27660108333332</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.470486690808767</v>
+        <v>0.5527657814274552</v>
       </c>
       <c r="T96">
-        <v>6.179708816262109</v>
+        <v>7.376969838786813</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.043875052606575</v>
+        <v>2.022360578368611</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07444478907137274</v>
+        <v>0.07434657669421947</v>
       </c>
       <c r="C97">
-        <v>167.0097834901997</v>
+        <v>155.1245647940079</v>
       </c>
       <c r="D97">
-        <v>1546.7847834902</v>
+        <v>1549.564564794008</v>
       </c>
       <c r="E97">
-        <v>611.9750000000001</v>
+        <v>626.6400000000001</v>
       </c>
       <c r="F97">
-        <v>1393.175</v>
+        <v>1407.84</v>
       </c>
       <c r="G97">
         <v>13.4</v>
@@ -9241,28 +9241,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M97">
-        <v>105.602665</v>
+        <v>106.714272</v>
       </c>
       <c r="N97">
-        <v>107.9640016666666</v>
+        <v>106.8523946666666</v>
       </c>
       <c r="O97">
-        <v>37.78740058333332</v>
+        <v>37.39833813333332</v>
       </c>
       <c r="P97">
-        <v>70.17660108333332</v>
+        <v>69.45405653333333</v>
       </c>
       <c r="Q97">
-        <v>70.27660108333332</v>
+        <v>69.55405653333332</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5527657814274552</v>
+        <v>0.6761844173554877</v>
       </c>
       <c r="T97">
-        <v>7.376969838786813</v>
+        <v>9.172861372573868</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.022360578368611</v>
+        <v>2.001294322343937</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07434657669421947</v>
+        <v>0.0832014643170662</v>
       </c>
       <c r="C98">
-        <v>155.1245647940082</v>
+        <v>-75.60801514380933</v>
       </c>
       <c r="D98">
-        <v>1549.564564794008</v>
+        <v>1333.49698485619</v>
       </c>
       <c r="E98">
-        <v>626.6399999999999</v>
+        <v>641.3049999999998</v>
       </c>
       <c r="F98">
-        <v>1407.84</v>
+        <v>1422.505</v>
       </c>
       <c r="G98">
         <v>13.4</v>
@@ -9323,45 +9323,45 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M98">
-        <v>106.714272</v>
+        <v>128.02545</v>
       </c>
       <c r="N98">
-        <v>106.8523946666667</v>
+        <v>85.54121666666668</v>
       </c>
       <c r="O98">
-        <v>37.39833813333333</v>
+        <v>29.93942583333334</v>
       </c>
       <c r="P98">
-        <v>69.45405653333333</v>
+        <v>55.60179083333335</v>
       </c>
       <c r="Q98">
-        <v>69.55405653333332</v>
+        <v>55.70179083333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6761844173554861</v>
+        <v>0.881882143902206</v>
       </c>
       <c r="T98">
-        <v>9.172861372573845</v>
+        <v>12.16601392888559</v>
       </c>
       <c r="U98">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V98">
         <v>0.35</v>
       </c>
       <c r="W98">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y98">
-        <v>2.001294322343938</v>
+        <v>1.668157906624556</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0832014643170662</v>
+        <v>0.08319555193991293</v>
       </c>
       <c r="C99">
-        <v>-75.60801514380933</v>
+        <v>-90.14885234861731</v>
       </c>
       <c r="D99">
-        <v>1333.49698485619</v>
+        <v>1333.621147651383</v>
       </c>
       <c r="E99">
-        <v>641.3049999999998</v>
+        <v>655.97</v>
       </c>
       <c r="F99">
-        <v>1422.505</v>
+        <v>1437.17</v>
       </c>
       <c r="G99">
         <v>13.4</v>
@@ -9405,28 +9405,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M99">
-        <v>128.02545</v>
+        <v>129.3453</v>
       </c>
       <c r="N99">
-        <v>85.54121666666668</v>
+        <v>84.22136666666665</v>
       </c>
       <c r="O99">
-        <v>29.93942583333334</v>
+        <v>29.47747833333333</v>
       </c>
       <c r="P99">
-        <v>55.60179083333335</v>
+        <v>54.74388833333333</v>
       </c>
       <c r="Q99">
-        <v>55.70179083333334</v>
+        <v>54.84388833333333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.881882143902206</v>
+        <v>1.293277596995646</v>
       </c>
       <c r="T99">
-        <v>12.16601392888559</v>
+        <v>18.15231904150908</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.668157906624556</v>
+        <v>1.651135887169203</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08319555193991293</v>
+        <v>0.08318963956275967</v>
       </c>
       <c r="C100">
-        <v>-90.14885234861731</v>
+        <v>-104.6896664295105</v>
       </c>
       <c r="D100">
-        <v>1333.621147651383</v>
+        <v>1333.745333570489</v>
       </c>
       <c r="E100">
-        <v>655.97</v>
+        <v>670.635</v>
       </c>
       <c r="F100">
-        <v>1437.17</v>
+        <v>1451.835</v>
       </c>
       <c r="G100">
         <v>13.4</v>
@@ -9487,28 +9487,28 @@
         <v>213.5666666666667</v>
       </c>
       <c r="M100">
-        <v>129.3453</v>
+        <v>130.66515</v>
       </c>
       <c r="N100">
-        <v>84.22136666666665</v>
+        <v>82.90151666666665</v>
       </c>
       <c r="O100">
-        <v>29.47747833333333</v>
+        <v>29.01553083333333</v>
       </c>
       <c r="P100">
-        <v>54.74388833333333</v>
+        <v>53.88598583333332</v>
       </c>
       <c r="Q100">
-        <v>54.84388833333333</v>
+        <v>53.98598583333332</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.293277596995646</v>
+        <v>2.527463956275965</v>
       </c>
       <c r="T100">
-        <v>18.15231904150908</v>
+        <v>36.11123437937957</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.651135887169203</v>
+        <v>1.634457746894766</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08318963956275967</v>
-      </c>
-      <c r="C101">
-        <v>-104.6896664295105</v>
-      </c>
-      <c r="D101">
-        <v>1333.745333570489</v>
-      </c>
-      <c r="E101">
-        <v>670.635</v>
-      </c>
-      <c r="F101">
-        <v>1451.835</v>
-      </c>
-      <c r="G101">
-        <v>13.4</v>
-      </c>
-      <c r="H101">
-        <v>685.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>213.6666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.09999999999999432</v>
-      </c>
-      <c r="L101">
-        <v>213.5666666666667</v>
-      </c>
-      <c r="M101">
-        <v>130.66515</v>
-      </c>
-      <c r="N101">
-        <v>82.90151666666665</v>
-      </c>
-      <c r="O101">
-        <v>29.01553083333333</v>
-      </c>
-      <c r="P101">
-        <v>53.88598583333332</v>
-      </c>
-      <c r="Q101">
-        <v>53.98598583333332</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.527463956275965</v>
-      </c>
-      <c r="T101">
-        <v>36.11123437937957</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.0585</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.634457746894766</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
